--- a/artfynd/A 57504-2024 artfynd.xlsx
+++ b/artfynd/A 57504-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1605,6 +1605,2822 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122773616</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Slåttmyrtjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>438161</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7010308</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122773625</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Slåttmyrtjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>438106</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7010492</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Hackande/trummande</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122773612</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Slåttmyrtjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>438085</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7010568</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122773604</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Slåttmyrtjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>438531</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7010323</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122773617</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Slåttmyrtjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>438166</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7010295</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122773599</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Slåttmyrtjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>438431</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7010633</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122773614</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Slåttmyrtjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>438145</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7010359</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>122773613</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Slåttmyrtjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>438083</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7010509</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>122773615</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Slåttmyrtjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>438145</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7010332</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>122773602</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Slåttmyrtjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>438601</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7010314</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>122773597</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Slåttmyrtjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>438355</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7010686</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>122773595</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Slåttmyrtjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>438193</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7010800</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>122773624</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57631</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Slåttmyrtjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>438215</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7010784</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Minst 6 st</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>122773605</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Slåttmyrtjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>438538</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7010447</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>122773618</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Slåttmyrtjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>438180</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7010258</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>122773596</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Slåttmyrtjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>438245</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7010805</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>122773600</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Slåttmyrtjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>438630</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7010427</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>122773619</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Slåttmyrtjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>438283</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7010189</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>122773607</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Slåttmyrtjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>438336</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7010625</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>122773592</v>
+      </c>
+      <c r="B29" t="n">
+        <v>90940</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Slåttmyrtjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>438283</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7010189</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>122773601</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Slåttmyrtjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>438600</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7010330</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>122773606</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Slåttmyrtjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>438521</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7010477</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Födosökte på flertalet träd och trummade</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>122773609</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Slåttmyrtjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>438318</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7010644</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>122773598</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Slåttmyrtjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>438360</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7010674</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>122773626</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78762</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Slåttmyrtjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>438169</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7010796</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>122773591</v>
+      </c>
+      <c r="B35" t="n">
+        <v>90940</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Slåttmyrtjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>438161</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7010308</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57504-2024 artfynd.xlsx
+++ b/artfynd/A 57504-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3874,7 +3874,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122773606</v>
+        <v>122773609</v>
       </c>
       <c r="B31" t="n">
         <v>57478</v>
@@ -3907,37 +3907,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>438521</v>
+        <v>438318</v>
       </c>
       <c r="R31" t="n">
-        <v>7010477</v>
+        <v>7010644</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3974,7 +3954,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Födosökte på flertalet träd och trummade</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4001,7 +3981,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122773609</v>
+        <v>122773598</v>
       </c>
       <c r="B32" t="n">
         <v>57478</v>
@@ -4041,10 +4021,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>438318</v>
+        <v>438360</v>
       </c>
       <c r="R32" t="n">
-        <v>7010644</v>
+        <v>7010674</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4108,10 +4088,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122773598</v>
+        <v>122773626</v>
       </c>
       <c r="B33" t="n">
-        <v>57478</v>
+        <v>78762</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4124,21 +4104,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4148,10 +4128,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>438360</v>
+        <v>438169</v>
       </c>
       <c r="R33" t="n">
-        <v>7010674</v>
+        <v>7010796</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4188,7 +4168,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4215,10 +4195,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122773626</v>
+        <v>122773591</v>
       </c>
       <c r="B34" t="n">
-        <v>78762</v>
+        <v>90940</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4231,21 +4211,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4255,10 +4235,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>438169</v>
+        <v>438161</v>
       </c>
       <c r="R34" t="n">
-        <v>7010796</v>
+        <v>7010308</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4291,11 +4271,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4322,10 +4297,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122773591</v>
+        <v>122797613</v>
       </c>
       <c r="B35" t="n">
-        <v>90940</v>
+        <v>57478</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4338,21 +4313,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4362,10 +4337,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>438161</v>
+        <v>438189</v>
       </c>
       <c r="R35" t="n">
-        <v>7010308</v>
+        <v>7010284</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4392,12 +4367,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4421,6 +4401,133 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>122773606</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Slåttmyrtjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>438521</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7010477</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Födosökte på flertalet träd och trummade. Hörde ev ytterligare en tretå i närheten samtidigt.</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57504-2024 artfynd.xlsx
+++ b/artfynd/A 57504-2024 artfynd.xlsx
@@ -1608,7 +1608,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122773616</v>
+        <v>122773598</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>438161</v>
+        <v>438360</v>
       </c>
       <c r="R10" t="n">
-        <v>7010308</v>
+        <v>7010674</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1715,10 +1715,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122773625</v>
+        <v>122773604</v>
       </c>
       <c r="B11" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1731,16 +1731,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1748,29 +1748,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>438106</v>
+        <v>438531</v>
       </c>
       <c r="R11" t="n">
-        <v>7010492</v>
+        <v>7010323</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1807,7 +1795,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Hackande/trummande</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1834,7 +1822,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122773612</v>
+        <v>122773613</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1874,10 +1862,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>438085</v>
+        <v>438083</v>
       </c>
       <c r="R12" t="n">
-        <v>7010568</v>
+        <v>7010509</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1914,7 +1902,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1941,7 +1929,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122773604</v>
+        <v>122773616</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1981,10 +1969,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>438531</v>
+        <v>438161</v>
       </c>
       <c r="R13" t="n">
-        <v>7010323</v>
+        <v>7010308</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2021,7 +2009,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2048,7 +2036,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122773617</v>
+        <v>122773614</v>
       </c>
       <c r="B14" t="n">
         <v>57478</v>
@@ -2088,10 +2076,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>438166</v>
+        <v>438145</v>
       </c>
       <c r="R14" t="n">
-        <v>7010295</v>
+        <v>7010359</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2128,7 +2116,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2155,7 +2143,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122773599</v>
+        <v>122773612</v>
       </c>
       <c r="B15" t="n">
         <v>57478</v>
@@ -2195,10 +2183,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>438431</v>
+        <v>438085</v>
       </c>
       <c r="R15" t="n">
-        <v>7010633</v>
+        <v>7010568</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2235,7 +2223,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2262,7 +2250,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122773614</v>
+        <v>122773619</v>
       </c>
       <c r="B16" t="n">
         <v>57478</v>
@@ -2302,10 +2290,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>438145</v>
+        <v>438283</v>
       </c>
       <c r="R16" t="n">
-        <v>7010359</v>
+        <v>7010189</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2342,7 +2330,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2369,7 +2357,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122773613</v>
+        <v>122773595</v>
       </c>
       <c r="B17" t="n">
         <v>57478</v>
@@ -2409,10 +2397,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>438083</v>
+        <v>438193</v>
       </c>
       <c r="R17" t="n">
-        <v>7010509</v>
+        <v>7010800</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2476,10 +2464,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122773615</v>
+        <v>122773592</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>90940</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2492,21 +2480,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2516,10 +2504,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>438145</v>
+        <v>438283</v>
       </c>
       <c r="R18" t="n">
-        <v>7010332</v>
+        <v>7010189</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2552,11 +2540,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2583,7 +2566,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122773602</v>
+        <v>122773599</v>
       </c>
       <c r="B19" t="n">
         <v>57478</v>
@@ -2623,10 +2606,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>438601</v>
+        <v>438431</v>
       </c>
       <c r="R19" t="n">
-        <v>7010314</v>
+        <v>7010633</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2663,7 +2646,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2690,7 +2673,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122773597</v>
+        <v>122773596</v>
       </c>
       <c r="B20" t="n">
         <v>57478</v>
@@ -2730,10 +2713,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>438355</v>
+        <v>438245</v>
       </c>
       <c r="R20" t="n">
-        <v>7010686</v>
+        <v>7010805</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2797,7 +2780,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122773595</v>
+        <v>122773601</v>
       </c>
       <c r="B21" t="n">
         <v>57478</v>
@@ -2837,10 +2820,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>438193</v>
+        <v>438600</v>
       </c>
       <c r="R21" t="n">
-        <v>7010800</v>
+        <v>7010330</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3023,10 +3006,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122773605</v>
+        <v>122773625</v>
       </c>
       <c r="B23" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3039,16 +3022,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3056,17 +3039,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>438538</v>
+        <v>438106</v>
       </c>
       <c r="R23" t="n">
-        <v>7010447</v>
+        <v>7010492</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3103,7 +3098,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Hackande/trummande</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3237,7 +3232,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122773596</v>
+        <v>122773615</v>
       </c>
       <c r="B25" t="n">
         <v>57478</v>
@@ -3277,10 +3272,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>438245</v>
+        <v>438145</v>
       </c>
       <c r="R25" t="n">
-        <v>7010805</v>
+        <v>7010332</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3317,7 +3312,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3344,7 +3339,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122773600</v>
+        <v>122773597</v>
       </c>
       <c r="B26" t="n">
         <v>57478</v>
@@ -3384,10 +3379,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>438630</v>
+        <v>438355</v>
       </c>
       <c r="R26" t="n">
-        <v>7010427</v>
+        <v>7010686</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3424,7 +3419,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3451,7 +3446,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122773619</v>
+        <v>122773609</v>
       </c>
       <c r="B27" t="n">
         <v>57478</v>
@@ -3491,10 +3486,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>438283</v>
+        <v>438318</v>
       </c>
       <c r="R27" t="n">
-        <v>7010189</v>
+        <v>7010644</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3531,7 +3526,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3665,10 +3660,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122773592</v>
+        <v>122773626</v>
       </c>
       <c r="B29" t="n">
-        <v>90940</v>
+        <v>78762</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3681,21 +3676,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3705,10 +3700,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>438283</v>
+        <v>438169</v>
       </c>
       <c r="R29" t="n">
-        <v>7010189</v>
+        <v>7010796</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3741,6 +3736,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3767,10 +3767,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122773601</v>
+        <v>122773591</v>
       </c>
       <c r="B30" t="n">
-        <v>57478</v>
+        <v>90940</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3783,21 +3783,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>438600</v>
+        <v>438161</v>
       </c>
       <c r="R30" t="n">
-        <v>7010330</v>
+        <v>7010308</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3843,11 +3843,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3874,7 +3869,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122773609</v>
+        <v>122773617</v>
       </c>
       <c r="B31" t="n">
         <v>57478</v>
@@ -3914,10 +3909,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>438318</v>
+        <v>438166</v>
       </c>
       <c r="R31" t="n">
-        <v>7010644</v>
+        <v>7010295</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3954,7 +3949,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3981,7 +3976,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122773598</v>
+        <v>122773605</v>
       </c>
       <c r="B32" t="n">
         <v>57478</v>
@@ -4021,10 +4016,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>438360</v>
+        <v>438538</v>
       </c>
       <c r="R32" t="n">
-        <v>7010674</v>
+        <v>7010447</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4061,7 +4056,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4088,10 +4083,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122773626</v>
+        <v>122773600</v>
       </c>
       <c r="B33" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4104,21 +4099,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4128,10 +4123,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>438169</v>
+        <v>438630</v>
       </c>
       <c r="R33" t="n">
-        <v>7010796</v>
+        <v>7010427</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4168,7 +4163,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4195,10 +4190,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122773591</v>
+        <v>122773602</v>
       </c>
       <c r="B34" t="n">
-        <v>90940</v>
+        <v>57478</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4211,21 +4206,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4235,10 +4230,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>438161</v>
+        <v>438601</v>
       </c>
       <c r="R34" t="n">
-        <v>7010308</v>
+        <v>7010314</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4271,6 +4266,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4297,7 +4297,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122797613</v>
+        <v>122773606</v>
       </c>
       <c r="B35" t="n">
         <v>57478</v>
@@ -4330,17 +4330,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>438189</v>
+        <v>438521</v>
       </c>
       <c r="R35" t="n">
-        <v>7010284</v>
+        <v>7010477</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4367,17 +4387,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Födosökte på flertalet träd och trummade. Hörde ev ytterligare en tretå i närheten samtidigt.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4404,7 +4424,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122773606</v>
+        <v>122797613</v>
       </c>
       <c r="B36" t="n">
         <v>57478</v>
@@ -4437,37 +4457,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>438521</v>
+        <v>438189</v>
       </c>
       <c r="R36" t="n">
-        <v>7010477</v>
+        <v>7010284</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4494,17 +4494,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Födosökte på flertalet träd och trummade. Hörde ev ytterligare en tretå i närheten samtidigt.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 57504-2024 artfynd.xlsx
+++ b/artfynd/A 57504-2024 artfynd.xlsx
@@ -1715,7 +1715,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122773604</v>
+        <v>122773595</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>438531</v>
+        <v>438193</v>
       </c>
       <c r="R11" t="n">
-        <v>7010323</v>
+        <v>7010800</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1822,7 +1822,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122773613</v>
+        <v>122773597</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>438083</v>
+        <v>438355</v>
       </c>
       <c r="R12" t="n">
-        <v>7010509</v>
+        <v>7010686</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1929,10 +1929,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122773616</v>
+        <v>122773591</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>90944</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1945,21 +1945,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2005,11 +2005,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2143,10 +2138,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122773612</v>
+        <v>122773626</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2159,21 +2154,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2183,10 +2178,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>438085</v>
+        <v>438169</v>
       </c>
       <c r="R15" t="n">
-        <v>7010568</v>
+        <v>7010796</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2223,7 +2218,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2250,10 +2245,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122773619</v>
+        <v>122773592</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>90944</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2266,21 +2261,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2326,11 +2321,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2357,7 +2347,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122773595</v>
+        <v>122773619</v>
       </c>
       <c r="B17" t="n">
         <v>57478</v>
@@ -2397,10 +2387,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>438193</v>
+        <v>438283</v>
       </c>
       <c r="R17" t="n">
-        <v>7010800</v>
+        <v>7010189</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2437,7 +2427,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2464,10 +2454,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122773592</v>
+        <v>122773616</v>
       </c>
       <c r="B18" t="n">
-        <v>90940</v>
+        <v>57478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2480,21 +2470,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2504,10 +2494,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>438283</v>
+        <v>438161</v>
       </c>
       <c r="R18" t="n">
-        <v>7010189</v>
+        <v>7010308</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2540,6 +2530,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2566,7 +2561,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122773599</v>
+        <v>122773613</v>
       </c>
       <c r="B19" t="n">
         <v>57478</v>
@@ -2606,10 +2601,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>438431</v>
+        <v>438083</v>
       </c>
       <c r="R19" t="n">
-        <v>7010633</v>
+        <v>7010509</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2673,7 +2668,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122773596</v>
+        <v>122773601</v>
       </c>
       <c r="B20" t="n">
         <v>57478</v>
@@ -2713,10 +2708,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>438245</v>
+        <v>438600</v>
       </c>
       <c r="R20" t="n">
-        <v>7010805</v>
+        <v>7010330</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2753,7 +2748,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2780,7 +2775,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122773601</v>
+        <v>122773602</v>
       </c>
       <c r="B21" t="n">
         <v>57478</v>
@@ -2820,10 +2815,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>438600</v>
+        <v>438601</v>
       </c>
       <c r="R21" t="n">
-        <v>7010330</v>
+        <v>7010314</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2860,7 +2855,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2887,10 +2882,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122773624</v>
+        <v>122773599</v>
       </c>
       <c r="B22" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2903,46 +2898,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>438215</v>
+        <v>438431</v>
       </c>
       <c r="R22" t="n">
-        <v>7010784</v>
+        <v>7010633</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2979,7 +2962,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Minst 6 st</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3006,10 +2989,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122773625</v>
+        <v>122773618</v>
       </c>
       <c r="B23" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3022,16 +3005,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3039,29 +3022,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>438106</v>
+        <v>438180</v>
       </c>
       <c r="R23" t="n">
-        <v>7010492</v>
+        <v>7010258</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3098,7 +3069,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Hackande/trummande</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3125,7 +3096,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122773618</v>
+        <v>122773607</v>
       </c>
       <c r="B24" t="n">
         <v>57478</v>
@@ -3165,10 +3136,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>438180</v>
+        <v>438336</v>
       </c>
       <c r="R24" t="n">
-        <v>7010258</v>
+        <v>7010625</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3205,7 +3176,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3232,7 +3203,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122773615</v>
+        <v>122773600</v>
       </c>
       <c r="B25" t="n">
         <v>57478</v>
@@ -3272,10 +3243,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>438145</v>
+        <v>438630</v>
       </c>
       <c r="R25" t="n">
-        <v>7010332</v>
+        <v>7010427</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3312,7 +3283,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3339,7 +3310,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122773597</v>
+        <v>122773617</v>
       </c>
       <c r="B26" t="n">
         <v>57478</v>
@@ -3379,10 +3350,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>438355</v>
+        <v>438166</v>
       </c>
       <c r="R26" t="n">
-        <v>7010686</v>
+        <v>7010295</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3446,10 +3417,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122773609</v>
+        <v>122773625</v>
       </c>
       <c r="B27" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3462,16 +3433,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3479,17 +3450,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>438318</v>
+        <v>438106</v>
       </c>
       <c r="R27" t="n">
-        <v>7010644</v>
+        <v>7010492</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3526,7 +3509,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hackande/trummande</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3553,7 +3536,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122773607</v>
+        <v>122773615</v>
       </c>
       <c r="B28" t="n">
         <v>57478</v>
@@ -3593,10 +3576,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>438336</v>
+        <v>438145</v>
       </c>
       <c r="R28" t="n">
-        <v>7010625</v>
+        <v>7010332</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3660,10 +3643,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122773626</v>
+        <v>122773596</v>
       </c>
       <c r="B29" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3676,21 +3659,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3700,10 +3683,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>438169</v>
+        <v>438245</v>
       </c>
       <c r="R29" t="n">
-        <v>7010796</v>
+        <v>7010805</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3740,7 +3723,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3767,10 +3750,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122773591</v>
+        <v>122773604</v>
       </c>
       <c r="B30" t="n">
-        <v>90940</v>
+        <v>57478</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3783,21 +3766,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3807,10 +3790,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>438161</v>
+        <v>438531</v>
       </c>
       <c r="R30" t="n">
-        <v>7010308</v>
+        <v>7010323</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3843,6 +3826,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3869,10 +3857,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122773617</v>
+        <v>122773624</v>
       </c>
       <c r="B31" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3885,34 +3873,46 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>438166</v>
+        <v>438215</v>
       </c>
       <c r="R31" t="n">
-        <v>7010295</v>
+        <v>7010784</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3949,7 +3949,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Minst 6 st</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3976,7 +3976,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122773605</v>
+        <v>122773612</v>
       </c>
       <c r="B32" t="n">
         <v>57478</v>
@@ -4016,10 +4016,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>438538</v>
+        <v>438085</v>
       </c>
       <c r="R32" t="n">
-        <v>7010447</v>
+        <v>7010568</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4083,7 +4083,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122773600</v>
+        <v>122773609</v>
       </c>
       <c r="B33" t="n">
         <v>57478</v>
@@ -4123,10 +4123,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>438630</v>
+        <v>438318</v>
       </c>
       <c r="R33" t="n">
-        <v>7010427</v>
+        <v>7010644</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4163,7 +4163,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4190,7 +4190,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122773602</v>
+        <v>122773605</v>
       </c>
       <c r="B34" t="n">
         <v>57478</v>
@@ -4230,10 +4230,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>438601</v>
+        <v>438538</v>
       </c>
       <c r="R34" t="n">
-        <v>7010314</v>
+        <v>7010447</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4297,7 +4297,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122773606</v>
+        <v>122797613</v>
       </c>
       <c r="B35" t="n">
         <v>57478</v>
@@ -4330,37 +4330,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>438521</v>
+        <v>438189</v>
       </c>
       <c r="R35" t="n">
-        <v>7010477</v>
+        <v>7010284</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4387,17 +4367,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Födosökte på flertalet träd och trummade. Hörde ev ytterligare en tretå i närheten samtidigt.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4424,7 +4404,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122797613</v>
+        <v>122773606</v>
       </c>
       <c r="B36" t="n">
         <v>57478</v>
@@ -4457,17 +4437,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>438189</v>
+        <v>438521</v>
       </c>
       <c r="R36" t="n">
-        <v>7010284</v>
+        <v>7010477</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4494,17 +4494,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Födosökte på flertalet träd och trummade. Hörde ev ytterligare en tretå i närheten samtidigt.</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 57504-2024 artfynd.xlsx
+++ b/artfynd/A 57504-2024 artfynd.xlsx
@@ -1608,7 +1608,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122773598</v>
+        <v>122773615</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>438360</v>
+        <v>438145</v>
       </c>
       <c r="R10" t="n">
-        <v>7010674</v>
+        <v>7010332</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1715,7 +1715,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122773595</v>
+        <v>122773607</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>438193</v>
+        <v>438336</v>
       </c>
       <c r="R11" t="n">
-        <v>7010800</v>
+        <v>7010625</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1822,7 +1822,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122773597</v>
+        <v>122773609</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>438355</v>
+        <v>438318</v>
       </c>
       <c r="R12" t="n">
-        <v>7010686</v>
+        <v>7010644</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2031,7 +2031,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122773614</v>
+        <v>122773599</v>
       </c>
       <c r="B14" t="n">
         <v>57478</v>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>438145</v>
+        <v>438431</v>
       </c>
       <c r="R14" t="n">
-        <v>7010359</v>
+        <v>7010633</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122773626</v>
+        <v>122773592</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>90944</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2154,21 +2154,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>438169</v>
+        <v>438283</v>
       </c>
       <c r="R15" t="n">
-        <v>7010796</v>
+        <v>7010189</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2214,11 +2214,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2245,10 +2240,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122773592</v>
+        <v>122773616</v>
       </c>
       <c r="B16" t="n">
-        <v>90944</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2261,21 +2256,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2285,10 +2280,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>438283</v>
+        <v>438161</v>
       </c>
       <c r="R16" t="n">
-        <v>7010189</v>
+        <v>7010308</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2321,6 +2316,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2347,7 +2347,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122773619</v>
+        <v>122773612</v>
       </c>
       <c r="B17" t="n">
         <v>57478</v>
@@ -2387,10 +2387,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>438283</v>
+        <v>438085</v>
       </c>
       <c r="R17" t="n">
-        <v>7010189</v>
+        <v>7010568</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2454,7 +2454,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122773616</v>
+        <v>122773596</v>
       </c>
       <c r="B18" t="n">
         <v>57478</v>
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>438161</v>
+        <v>438245</v>
       </c>
       <c r="R18" t="n">
-        <v>7010308</v>
+        <v>7010805</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2561,7 +2561,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122773613</v>
+        <v>122773598</v>
       </c>
       <c r="B19" t="n">
         <v>57478</v>
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>438083</v>
+        <v>438360</v>
       </c>
       <c r="R19" t="n">
-        <v>7010509</v>
+        <v>7010674</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2668,7 +2668,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122773601</v>
+        <v>122773619</v>
       </c>
       <c r="B20" t="n">
         <v>57478</v>
@@ -2708,10 +2708,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>438600</v>
+        <v>438283</v>
       </c>
       <c r="R20" t="n">
-        <v>7010330</v>
+        <v>7010189</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2775,7 +2775,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122773602</v>
+        <v>122773601</v>
       </c>
       <c r="B21" t="n">
         <v>57478</v>
@@ -2815,10 +2815,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>438601</v>
+        <v>438600</v>
       </c>
       <c r="R21" t="n">
-        <v>7010314</v>
+        <v>7010330</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2882,7 +2882,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122773599</v>
+        <v>122773618</v>
       </c>
       <c r="B22" t="n">
         <v>57478</v>
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>438431</v>
+        <v>438180</v>
       </c>
       <c r="R22" t="n">
-        <v>7010633</v>
+        <v>7010258</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2989,7 +2989,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122773618</v>
+        <v>122773613</v>
       </c>
       <c r="B23" t="n">
         <v>57478</v>
@@ -3029,10 +3029,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>438180</v>
+        <v>438083</v>
       </c>
       <c r="R23" t="n">
-        <v>7010258</v>
+        <v>7010509</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3096,7 +3096,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122773607</v>
+        <v>122773617</v>
       </c>
       <c r="B24" t="n">
         <v>57478</v>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>438336</v>
+        <v>438166</v>
       </c>
       <c r="R24" t="n">
-        <v>7010625</v>
+        <v>7010295</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3203,10 +3203,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122773600</v>
+        <v>122773625</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3219,16 +3219,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3236,17 +3236,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>438630</v>
+        <v>438106</v>
       </c>
       <c r="R25" t="n">
-        <v>7010427</v>
+        <v>7010492</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3283,7 +3295,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hackande/trummande</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3310,7 +3322,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122773617</v>
+        <v>122773605</v>
       </c>
       <c r="B26" t="n">
         <v>57478</v>
@@ -3350,10 +3362,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>438166</v>
+        <v>438538</v>
       </c>
       <c r="R26" t="n">
-        <v>7010295</v>
+        <v>7010447</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3390,7 +3402,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3417,10 +3429,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122773625</v>
+        <v>122773614</v>
       </c>
       <c r="B27" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3433,16 +3445,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3450,29 +3462,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>438106</v>
+        <v>438145</v>
       </c>
       <c r="R27" t="n">
-        <v>7010492</v>
+        <v>7010359</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Hackande/trummande</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3536,7 +3536,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122773615</v>
+        <v>122773597</v>
       </c>
       <c r="B28" t="n">
         <v>57478</v>
@@ -3576,10 +3576,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>438145</v>
+        <v>438355</v>
       </c>
       <c r="R28" t="n">
-        <v>7010332</v>
+        <v>7010686</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3643,7 +3643,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122773596</v>
+        <v>122773595</v>
       </c>
       <c r="B29" t="n">
         <v>57478</v>
@@ -3683,10 +3683,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>438245</v>
+        <v>438193</v>
       </c>
       <c r="R29" t="n">
-        <v>7010805</v>
+        <v>7010800</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3750,10 +3750,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122773604</v>
+        <v>122773626</v>
       </c>
       <c r="B30" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3766,21 +3766,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>438531</v>
+        <v>438169</v>
       </c>
       <c r="R30" t="n">
-        <v>7010323</v>
+        <v>7010796</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3976,7 +3976,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122773612</v>
+        <v>122773600</v>
       </c>
       <c r="B32" t="n">
         <v>57478</v>
@@ -4016,10 +4016,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>438085</v>
+        <v>438630</v>
       </c>
       <c r="R32" t="n">
-        <v>7010568</v>
+        <v>7010427</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4083,7 +4083,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122773609</v>
+        <v>122773602</v>
       </c>
       <c r="B33" t="n">
         <v>57478</v>
@@ -4123,10 +4123,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>438318</v>
+        <v>438601</v>
       </c>
       <c r="R33" t="n">
-        <v>7010644</v>
+        <v>7010314</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4163,7 +4163,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4190,7 +4190,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122773605</v>
+        <v>122773604</v>
       </c>
       <c r="B34" t="n">
         <v>57478</v>
@@ -4230,10 +4230,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>438538</v>
+        <v>438531</v>
       </c>
       <c r="R34" t="n">
-        <v>7010447</v>
+        <v>7010323</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4297,7 +4297,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122797613</v>
+        <v>122773606</v>
       </c>
       <c r="B35" t="n">
         <v>57478</v>
@@ -4330,17 +4330,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>438189</v>
+        <v>438521</v>
       </c>
       <c r="R35" t="n">
-        <v>7010284</v>
+        <v>7010477</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4367,17 +4387,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Födosökte på flertalet träd och trummade. Hörde ev ytterligare en tretå i närheten samtidigt.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4404,7 +4424,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122773606</v>
+        <v>122797613</v>
       </c>
       <c r="B36" t="n">
         <v>57478</v>
@@ -4437,37 +4457,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>438521</v>
+        <v>438189</v>
       </c>
       <c r="R36" t="n">
-        <v>7010477</v>
+        <v>7010284</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4494,17 +4494,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Födosökte på flertalet träd och trummade. Hörde ev ytterligare en tretå i närheten samtidigt.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 57504-2024 artfynd.xlsx
+++ b/artfynd/A 57504-2024 artfynd.xlsx
@@ -1608,7 +1608,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122773615</v>
+        <v>122773598</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>438145</v>
+        <v>438360</v>
       </c>
       <c r="R10" t="n">
-        <v>7010332</v>
+        <v>7010674</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1715,7 +1715,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122773607</v>
+        <v>122773601</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>438336</v>
+        <v>438600</v>
       </c>
       <c r="R11" t="n">
-        <v>7010625</v>
+        <v>7010330</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122773609</v>
+        <v>122773592</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>90944</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1838,21 +1838,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>438318</v>
+        <v>438283</v>
       </c>
       <c r="R12" t="n">
-        <v>7010644</v>
+        <v>7010189</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1898,11 +1898,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1929,10 +1924,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122773591</v>
+        <v>122773596</v>
       </c>
       <c r="B13" t="n">
-        <v>90944</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1945,21 +1940,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1969,10 +1964,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>438161</v>
+        <v>438245</v>
       </c>
       <c r="R13" t="n">
-        <v>7010308</v>
+        <v>7010805</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2005,6 +2000,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2031,10 +2031,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122773599</v>
+        <v>122773591</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>90944</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2047,21 +2047,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>438431</v>
+        <v>438161</v>
       </c>
       <c r="R14" t="n">
-        <v>7010633</v>
+        <v>7010308</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2107,11 +2107,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2138,10 +2133,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122773592</v>
+        <v>122773597</v>
       </c>
       <c r="B15" t="n">
-        <v>90944</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2154,21 +2149,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2178,10 +2173,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>438283</v>
+        <v>438355</v>
       </c>
       <c r="R15" t="n">
-        <v>7010189</v>
+        <v>7010686</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2214,6 +2209,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2240,7 +2240,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122773616</v>
+        <v>122773618</v>
       </c>
       <c r="B16" t="n">
         <v>57478</v>
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>438161</v>
+        <v>438180</v>
       </c>
       <c r="R16" t="n">
-        <v>7010308</v>
+        <v>7010258</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2347,7 +2347,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122773612</v>
+        <v>122773605</v>
       </c>
       <c r="B17" t="n">
         <v>57478</v>
@@ -2387,10 +2387,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>438085</v>
+        <v>438538</v>
       </c>
       <c r="R17" t="n">
-        <v>7010568</v>
+        <v>7010447</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2454,7 +2454,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122773596</v>
+        <v>122773604</v>
       </c>
       <c r="B18" t="n">
         <v>57478</v>
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>438245</v>
+        <v>438531</v>
       </c>
       <c r="R18" t="n">
-        <v>7010805</v>
+        <v>7010323</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2561,7 +2561,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122773598</v>
+        <v>122773613</v>
       </c>
       <c r="B19" t="n">
         <v>57478</v>
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>438360</v>
+        <v>438083</v>
       </c>
       <c r="R19" t="n">
-        <v>7010674</v>
+        <v>7010509</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2668,7 +2668,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122773619</v>
+        <v>122773612</v>
       </c>
       <c r="B20" t="n">
         <v>57478</v>
@@ -2708,10 +2708,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>438283</v>
+        <v>438085</v>
       </c>
       <c r="R20" t="n">
-        <v>7010189</v>
+        <v>7010568</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2775,7 +2775,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122773601</v>
+        <v>122773595</v>
       </c>
       <c r="B21" t="n">
         <v>57478</v>
@@ -2815,10 +2815,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>438600</v>
+        <v>438193</v>
       </c>
       <c r="R21" t="n">
-        <v>7010330</v>
+        <v>7010800</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2882,7 +2882,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122773618</v>
+        <v>122773619</v>
       </c>
       <c r="B22" t="n">
         <v>57478</v>
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>438180</v>
+        <v>438283</v>
       </c>
       <c r="R22" t="n">
-        <v>7010258</v>
+        <v>7010189</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2989,7 +2989,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122773613</v>
+        <v>122773615</v>
       </c>
       <c r="B23" t="n">
         <v>57478</v>
@@ -3029,10 +3029,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>438083</v>
+        <v>438145</v>
       </c>
       <c r="R23" t="n">
-        <v>7010509</v>
+        <v>7010332</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3096,7 +3096,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122773617</v>
+        <v>122773600</v>
       </c>
       <c r="B24" t="n">
         <v>57478</v>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>438166</v>
+        <v>438630</v>
       </c>
       <c r="R24" t="n">
-        <v>7010295</v>
+        <v>7010427</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3203,10 +3203,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122773625</v>
+        <v>122773616</v>
       </c>
       <c r="B25" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3219,16 +3219,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3236,29 +3236,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>438106</v>
+        <v>438161</v>
       </c>
       <c r="R25" t="n">
-        <v>7010492</v>
+        <v>7010308</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3295,7 +3283,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Hackande/trummande</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3322,7 +3310,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122773605</v>
+        <v>122773607</v>
       </c>
       <c r="B26" t="n">
         <v>57478</v>
@@ -3362,10 +3350,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>438538</v>
+        <v>438336</v>
       </c>
       <c r="R26" t="n">
-        <v>7010447</v>
+        <v>7010625</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3402,7 +3390,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3429,10 +3417,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122773614</v>
+        <v>122773626</v>
       </c>
       <c r="B27" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3445,21 +3433,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3469,10 +3457,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>438145</v>
+        <v>438169</v>
       </c>
       <c r="R27" t="n">
-        <v>7010359</v>
+        <v>7010796</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3509,7 +3497,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3536,10 +3524,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122773597</v>
+        <v>122773625</v>
       </c>
       <c r="B28" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3552,16 +3540,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3569,17 +3557,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>438355</v>
+        <v>438106</v>
       </c>
       <c r="R28" t="n">
-        <v>7010686</v>
+        <v>7010492</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Hackande/trummande</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3643,10 +3643,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122773595</v>
+        <v>122773624</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3659,34 +3659,46 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>438193</v>
+        <v>438215</v>
       </c>
       <c r="R29" t="n">
-        <v>7010800</v>
+        <v>7010784</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3723,7 +3735,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 6 st</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3750,10 +3762,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122773626</v>
+        <v>122773609</v>
       </c>
       <c r="B30" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3766,21 +3778,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3790,10 +3802,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>438169</v>
+        <v>438318</v>
       </c>
       <c r="R30" t="n">
-        <v>7010796</v>
+        <v>7010644</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3830,7 +3842,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3857,10 +3869,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122773624</v>
+        <v>122773602</v>
       </c>
       <c r="B31" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3873,46 +3885,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>438215</v>
+        <v>438601</v>
       </c>
       <c r="R31" t="n">
-        <v>7010784</v>
+        <v>7010314</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3949,7 +3949,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Minst 6 st</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3976,7 +3976,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122773600</v>
+        <v>122773614</v>
       </c>
       <c r="B32" t="n">
         <v>57478</v>
@@ -4016,10 +4016,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>438630</v>
+        <v>438145</v>
       </c>
       <c r="R32" t="n">
-        <v>7010427</v>
+        <v>7010359</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4083,7 +4083,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122773602</v>
+        <v>122773617</v>
       </c>
       <c r="B33" t="n">
         <v>57478</v>
@@ -4123,10 +4123,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>438601</v>
+        <v>438166</v>
       </c>
       <c r="R33" t="n">
-        <v>7010314</v>
+        <v>7010295</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4190,7 +4190,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122773604</v>
+        <v>122773599</v>
       </c>
       <c r="B34" t="n">
         <v>57478</v>
@@ -4230,10 +4230,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>438531</v>
+        <v>438431</v>
       </c>
       <c r="R34" t="n">
-        <v>7010323</v>
+        <v>7010633</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4297,7 +4297,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122773606</v>
+        <v>122797613</v>
       </c>
       <c r="B35" t="n">
         <v>57478</v>
@@ -4330,37 +4330,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>438521</v>
+        <v>438189</v>
       </c>
       <c r="R35" t="n">
-        <v>7010477</v>
+        <v>7010284</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4387,17 +4367,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Födosökte på flertalet träd och trummade. Hörde ev ytterligare en tretå i närheten samtidigt.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4424,7 +4404,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122797613</v>
+        <v>122773606</v>
       </c>
       <c r="B36" t="n">
         <v>57478</v>
@@ -4457,17 +4437,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>438189</v>
+        <v>438521</v>
       </c>
       <c r="R36" t="n">
-        <v>7010284</v>
+        <v>7010477</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4494,17 +4494,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Födosökte på flertalet träd och trummade. Hörde ev ytterligare en tretå i närheten samtidigt.</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 57504-2024 artfynd.xlsx
+++ b/artfynd/A 57504-2024 artfynd.xlsx
@@ -3417,10 +3417,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122773626</v>
+        <v>122773625</v>
       </c>
       <c r="B27" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3433,34 +3433,46 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>438169</v>
+        <v>438106</v>
       </c>
       <c r="R27" t="n">
-        <v>7010796</v>
+        <v>7010492</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3497,7 +3509,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Hackande/trummande</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3524,10 +3536,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122773625</v>
+        <v>122773626</v>
       </c>
       <c r="B28" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3540,46 +3552,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>438106</v>
+        <v>438169</v>
       </c>
       <c r="R28" t="n">
-        <v>7010492</v>
+        <v>7010796</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Hackande/trummande</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 57504-2024 artfynd.xlsx
+++ b/artfynd/A 57504-2024 artfynd.xlsx
@@ -1608,7 +1608,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122773598</v>
+        <v>122773607</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>438360</v>
+        <v>438336</v>
       </c>
       <c r="R10" t="n">
-        <v>7010674</v>
+        <v>7010625</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1715,7 +1715,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122773601</v>
+        <v>122773609</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>438600</v>
+        <v>438318</v>
       </c>
       <c r="R11" t="n">
-        <v>7010330</v>
+        <v>7010644</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122773592</v>
+        <v>122773624</v>
       </c>
       <c r="B12" t="n">
-        <v>90944</v>
+        <v>57631</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1838,34 +1838,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>438283</v>
+        <v>438215</v>
       </c>
       <c r="R12" t="n">
-        <v>7010189</v>
+        <v>7010784</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1898,6 +1910,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Minst 6 st</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1924,10 +1941,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122773596</v>
+        <v>122773625</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1940,16 +1957,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1957,17 +1974,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>438245</v>
+        <v>438106</v>
       </c>
       <c r="R13" t="n">
-        <v>7010805</v>
+        <v>7010492</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2004,7 +2033,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Hackande/trummande</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2031,10 +2060,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122773591</v>
+        <v>122773602</v>
       </c>
       <c r="B14" t="n">
-        <v>90944</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2047,21 +2076,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2071,10 +2100,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>438161</v>
+        <v>438601</v>
       </c>
       <c r="R14" t="n">
-        <v>7010308</v>
+        <v>7010314</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2107,6 +2136,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2133,7 +2167,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122773597</v>
+        <v>122773604</v>
       </c>
       <c r="B15" t="n">
         <v>57478</v>
@@ -2173,10 +2207,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>438355</v>
+        <v>438531</v>
       </c>
       <c r="R15" t="n">
-        <v>7010686</v>
+        <v>7010323</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2213,7 +2247,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2240,7 +2274,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122773618</v>
+        <v>122773613</v>
       </c>
       <c r="B16" t="n">
         <v>57478</v>
@@ -2280,10 +2314,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>438180</v>
+        <v>438083</v>
       </c>
       <c r="R16" t="n">
-        <v>7010258</v>
+        <v>7010509</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2320,7 +2354,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2347,7 +2381,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122773605</v>
+        <v>122773617</v>
       </c>
       <c r="B17" t="n">
         <v>57478</v>
@@ -2387,10 +2421,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>438538</v>
+        <v>438166</v>
       </c>
       <c r="R17" t="n">
-        <v>7010447</v>
+        <v>7010295</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2427,7 +2461,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2454,7 +2488,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122773604</v>
+        <v>122773615</v>
       </c>
       <c r="B18" t="n">
         <v>57478</v>
@@ -2494,10 +2528,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>438531</v>
+        <v>438145</v>
       </c>
       <c r="R18" t="n">
-        <v>7010323</v>
+        <v>7010332</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2561,7 +2595,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122773613</v>
+        <v>122773597</v>
       </c>
       <c r="B19" t="n">
         <v>57478</v>
@@ -2601,10 +2635,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>438083</v>
+        <v>438355</v>
       </c>
       <c r="R19" t="n">
-        <v>7010509</v>
+        <v>7010686</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2641,7 +2675,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2668,7 +2702,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122773612</v>
+        <v>122773616</v>
       </c>
       <c r="B20" t="n">
         <v>57478</v>
@@ -2708,10 +2742,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>438085</v>
+        <v>438161</v>
       </c>
       <c r="R20" t="n">
-        <v>7010568</v>
+        <v>7010308</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2748,7 +2782,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2775,10 +2809,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122773595</v>
+        <v>122773626</v>
       </c>
       <c r="B21" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2791,21 +2825,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2815,10 +2849,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>438193</v>
+        <v>438169</v>
       </c>
       <c r="R21" t="n">
-        <v>7010800</v>
+        <v>7010796</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2855,7 +2889,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2882,7 +2916,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122773619</v>
+        <v>122773598</v>
       </c>
       <c r="B22" t="n">
         <v>57478</v>
@@ -2922,10 +2956,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>438283</v>
+        <v>438360</v>
       </c>
       <c r="R22" t="n">
-        <v>7010189</v>
+        <v>7010674</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2962,7 +2996,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2989,7 +3023,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122773615</v>
+        <v>122773612</v>
       </c>
       <c r="B23" t="n">
         <v>57478</v>
@@ -3029,10 +3063,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>438145</v>
+        <v>438085</v>
       </c>
       <c r="R23" t="n">
-        <v>7010332</v>
+        <v>7010568</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3069,7 +3103,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3096,7 +3130,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122773600</v>
+        <v>122773605</v>
       </c>
       <c r="B24" t="n">
         <v>57478</v>
@@ -3136,10 +3170,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>438630</v>
+        <v>438538</v>
       </c>
       <c r="R24" t="n">
-        <v>7010427</v>
+        <v>7010447</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3176,7 +3210,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3203,7 +3237,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122773616</v>
+        <v>122773595</v>
       </c>
       <c r="B25" t="n">
         <v>57478</v>
@@ -3243,10 +3277,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>438161</v>
+        <v>438193</v>
       </c>
       <c r="R25" t="n">
-        <v>7010308</v>
+        <v>7010800</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3283,7 +3317,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3310,7 +3344,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122773607</v>
+        <v>122773619</v>
       </c>
       <c r="B26" t="n">
         <v>57478</v>
@@ -3350,10 +3384,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>438336</v>
+        <v>438283</v>
       </c>
       <c r="R26" t="n">
-        <v>7010625</v>
+        <v>7010189</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3390,7 +3424,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3417,10 +3451,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122773625</v>
+        <v>122773591</v>
       </c>
       <c r="B27" t="n">
-        <v>57494</v>
+        <v>90944</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3433,46 +3467,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>438106</v>
+        <v>438161</v>
       </c>
       <c r="R27" t="n">
-        <v>7010492</v>
+        <v>7010308</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3505,11 +3527,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Hackande/trummande</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3536,10 +3553,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122773626</v>
+        <v>122773592</v>
       </c>
       <c r="B28" t="n">
-        <v>78766</v>
+        <v>90944</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3552,21 +3569,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3576,10 +3593,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>438169</v>
+        <v>438283</v>
       </c>
       <c r="R28" t="n">
-        <v>7010796</v>
+        <v>7010189</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3612,11 +3629,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3643,10 +3655,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122773624</v>
+        <v>122773600</v>
       </c>
       <c r="B29" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3659,46 +3671,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>438215</v>
+        <v>438630</v>
       </c>
       <c r="R29" t="n">
-        <v>7010784</v>
+        <v>7010427</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Minst 6 st</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3762,7 +3762,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122773609</v>
+        <v>122773618</v>
       </c>
       <c r="B30" t="n">
         <v>57478</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>438318</v>
+        <v>438180</v>
       </c>
       <c r="R30" t="n">
-        <v>7010644</v>
+        <v>7010258</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3869,7 +3869,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122773602</v>
+        <v>122773614</v>
       </c>
       <c r="B31" t="n">
         <v>57478</v>
@@ -3909,10 +3909,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>438601</v>
+        <v>438145</v>
       </c>
       <c r="R31" t="n">
-        <v>7010314</v>
+        <v>7010359</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3949,7 +3949,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3976,7 +3976,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122773614</v>
+        <v>122773601</v>
       </c>
       <c r="B32" t="n">
         <v>57478</v>
@@ -4016,10 +4016,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>438145</v>
+        <v>438600</v>
       </c>
       <c r="R32" t="n">
-        <v>7010359</v>
+        <v>7010330</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4083,7 +4083,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122773617</v>
+        <v>122773596</v>
       </c>
       <c r="B33" t="n">
         <v>57478</v>
@@ -4123,10 +4123,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>438166</v>
+        <v>438245</v>
       </c>
       <c r="R33" t="n">
-        <v>7010295</v>
+        <v>7010805</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4297,7 +4297,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122797613</v>
+        <v>122773606</v>
       </c>
       <c r="B35" t="n">
         <v>57478</v>
@@ -4330,17 +4330,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>438189</v>
+        <v>438521</v>
       </c>
       <c r="R35" t="n">
-        <v>7010284</v>
+        <v>7010477</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4367,17 +4387,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Födosökte på flertalet träd och trummade. Hörde ev ytterligare en tretå i närheten samtidigt.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4404,7 +4424,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122773606</v>
+        <v>122797613</v>
       </c>
       <c r="B36" t="n">
         <v>57478</v>
@@ -4437,37 +4457,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>438521</v>
+        <v>438189</v>
       </c>
       <c r="R36" t="n">
-        <v>7010477</v>
+        <v>7010284</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4494,17 +4494,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Födosökte på flertalet träd och trummade. Hörde ev ytterligare en tretå i närheten samtidigt.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 57504-2024 artfynd.xlsx
+++ b/artfynd/A 57504-2024 artfynd.xlsx
@@ -1941,10 +1941,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122773625</v>
+        <v>122773602</v>
       </c>
       <c r="B13" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1957,16 +1957,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1974,29 +1974,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>438106</v>
+        <v>438601</v>
       </c>
       <c r="R13" t="n">
-        <v>7010492</v>
+        <v>7010314</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2033,7 +2021,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Hackande/trummande</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2060,10 +2048,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122773602</v>
+        <v>122773625</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2076,16 +2064,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2093,17 +2081,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>438601</v>
+        <v>438106</v>
       </c>
       <c r="R14" t="n">
-        <v>7010314</v>
+        <v>7010492</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Hackande/trummande</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -4297,7 +4297,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122773606</v>
+        <v>122797613</v>
       </c>
       <c r="B35" t="n">
         <v>57478</v>
@@ -4330,37 +4330,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>438521</v>
+        <v>438189</v>
       </c>
       <c r="R35" t="n">
-        <v>7010477</v>
+        <v>7010284</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4387,17 +4367,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Födosökte på flertalet träd och trummade. Hörde ev ytterligare en tretå i närheten samtidigt.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4424,14 +4404,14 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122797613</v>
+        <v>122773606</v>
       </c>
       <c r="B36" t="n">
         <v>57478</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4457,17 +4437,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>438189</v>
+        <v>438521</v>
       </c>
       <c r="R36" t="n">
-        <v>7010284</v>
+        <v>7010477</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4494,17 +4494,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Födosökte på flertalet träd och trummade. Hörde ev ytterligare en tretå i närheten samtidigt.</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 57504-2024 artfynd.xlsx
+++ b/artfynd/A 57504-2024 artfynd.xlsx
@@ -2809,10 +2809,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122773626</v>
+        <v>122773598</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2825,21 +2825,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>438169</v>
+        <v>438360</v>
       </c>
       <c r="R21" t="n">
-        <v>7010796</v>
+        <v>7010674</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2916,7 +2916,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122773598</v>
+        <v>122773612</v>
       </c>
       <c r="B22" t="n">
         <v>57478</v>
@@ -2956,10 +2956,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>438360</v>
+        <v>438085</v>
       </c>
       <c r="R22" t="n">
-        <v>7010674</v>
+        <v>7010568</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3023,7 +3023,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122773612</v>
+        <v>122773605</v>
       </c>
       <c r="B23" t="n">
         <v>57478</v>
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>438085</v>
+        <v>438538</v>
       </c>
       <c r="R23" t="n">
-        <v>7010568</v>
+        <v>7010447</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3130,10 +3130,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122773605</v>
+        <v>122773626</v>
       </c>
       <c r="B24" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3146,21 +3146,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3170,10 +3170,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>438538</v>
+        <v>438169</v>
       </c>
       <c r="R24" t="n">
-        <v>7010447</v>
+        <v>7010796</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 57504-2024 artfynd.xlsx
+++ b/artfynd/A 57504-2024 artfynd.xlsx
@@ -1608,7 +1608,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122773607</v>
+        <v>122773599</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>438336</v>
+        <v>438431</v>
       </c>
       <c r="R10" t="n">
-        <v>7010625</v>
+        <v>7010633</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1715,7 +1715,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122773609</v>
+        <v>122773616</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>438318</v>
+        <v>438161</v>
       </c>
       <c r="R11" t="n">
-        <v>7010644</v>
+        <v>7010308</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1822,10 +1822,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122773624</v>
+        <v>122773604</v>
       </c>
       <c r="B12" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1838,46 +1838,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>438215</v>
+        <v>438531</v>
       </c>
       <c r="R12" t="n">
-        <v>7010784</v>
+        <v>7010323</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1914,7 +1902,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Minst 6 st</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1941,7 +1929,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122773602</v>
+        <v>122773619</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1981,10 +1969,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>438601</v>
+        <v>438283</v>
       </c>
       <c r="R13" t="n">
-        <v>7010314</v>
+        <v>7010189</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2021,7 +2009,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2048,10 +2036,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122773625</v>
+        <v>122773592</v>
       </c>
       <c r="B14" t="n">
-        <v>57494</v>
+        <v>90952</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2064,46 +2052,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>438106</v>
+        <v>438283</v>
       </c>
       <c r="R14" t="n">
-        <v>7010492</v>
+        <v>7010189</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2136,11 +2112,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Hackande/trummande</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2167,7 +2138,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122773604</v>
+        <v>122773609</v>
       </c>
       <c r="B15" t="n">
         <v>57478</v>
@@ -2207,10 +2178,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>438531</v>
+        <v>438318</v>
       </c>
       <c r="R15" t="n">
-        <v>7010323</v>
+        <v>7010644</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2274,7 +2245,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122773613</v>
+        <v>122773617</v>
       </c>
       <c r="B16" t="n">
         <v>57478</v>
@@ -2314,10 +2285,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>438083</v>
+        <v>438166</v>
       </c>
       <c r="R16" t="n">
-        <v>7010509</v>
+        <v>7010295</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2354,7 +2325,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2381,7 +2352,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122773617</v>
+        <v>122773597</v>
       </c>
       <c r="B17" t="n">
         <v>57478</v>
@@ -2421,10 +2392,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>438166</v>
+        <v>438355</v>
       </c>
       <c r="R17" t="n">
-        <v>7010295</v>
+        <v>7010686</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2488,7 +2459,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122773615</v>
+        <v>122773598</v>
       </c>
       <c r="B18" t="n">
         <v>57478</v>
@@ -2528,10 +2499,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>438145</v>
+        <v>438360</v>
       </c>
       <c r="R18" t="n">
-        <v>7010332</v>
+        <v>7010674</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2595,7 +2566,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122773597</v>
+        <v>122773595</v>
       </c>
       <c r="B19" t="n">
         <v>57478</v>
@@ -2635,10 +2606,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>438355</v>
+        <v>438193</v>
       </c>
       <c r="R19" t="n">
-        <v>7010686</v>
+        <v>7010800</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2675,7 +2646,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2702,7 +2673,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122773616</v>
+        <v>122773601</v>
       </c>
       <c r="B20" t="n">
         <v>57478</v>
@@ -2742,10 +2713,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>438161</v>
+        <v>438600</v>
       </c>
       <c r="R20" t="n">
-        <v>7010308</v>
+        <v>7010330</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2782,7 +2753,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2809,10 +2780,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122773598</v>
+        <v>122773624</v>
       </c>
       <c r="B21" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2825,34 +2796,46 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>438360</v>
+        <v>438215</v>
       </c>
       <c r="R21" t="n">
-        <v>7010674</v>
+        <v>7010784</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2889,7 +2872,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 6 st</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2916,7 +2899,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122773612</v>
+        <v>122773618</v>
       </c>
       <c r="B22" t="n">
         <v>57478</v>
@@ -2956,10 +2939,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>438085</v>
+        <v>438180</v>
       </c>
       <c r="R22" t="n">
-        <v>7010568</v>
+        <v>7010258</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3023,7 +3006,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122773605</v>
+        <v>122773614</v>
       </c>
       <c r="B23" t="n">
         <v>57478</v>
@@ -3063,10 +3046,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>438538</v>
+        <v>438145</v>
       </c>
       <c r="R23" t="n">
-        <v>7010447</v>
+        <v>7010359</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3103,7 +3086,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3130,10 +3113,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122773626</v>
+        <v>122773613</v>
       </c>
       <c r="B24" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3146,21 +3129,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3170,10 +3153,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>438169</v>
+        <v>438083</v>
       </c>
       <c r="R24" t="n">
-        <v>7010796</v>
+        <v>7010509</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3210,7 +3193,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3237,10 +3220,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122773595</v>
+        <v>122773626</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3253,21 +3236,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3277,10 +3260,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>438193</v>
+        <v>438169</v>
       </c>
       <c r="R25" t="n">
-        <v>7010800</v>
+        <v>7010796</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3317,7 +3300,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3344,10 +3327,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122773619</v>
+        <v>122773591</v>
       </c>
       <c r="B26" t="n">
-        <v>57478</v>
+        <v>90952</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3360,21 +3343,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3384,10 +3367,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>438283</v>
+        <v>438161</v>
       </c>
       <c r="R26" t="n">
-        <v>7010189</v>
+        <v>7010308</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3420,11 +3403,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3451,10 +3429,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122773591</v>
+        <v>122773605</v>
       </c>
       <c r="B27" t="n">
-        <v>90944</v>
+        <v>57478</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3467,21 +3445,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3491,10 +3469,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>438161</v>
+        <v>438538</v>
       </c>
       <c r="R27" t="n">
-        <v>7010308</v>
+        <v>7010447</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3527,6 +3505,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3553,10 +3536,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122773592</v>
+        <v>122773625</v>
       </c>
       <c r="B28" t="n">
-        <v>90944</v>
+        <v>57494</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3569,34 +3552,46 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>438283</v>
+        <v>438106</v>
       </c>
       <c r="R28" t="n">
-        <v>7010189</v>
+        <v>7010492</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3629,6 +3624,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Hackande/trummande</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3655,7 +3655,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122773600</v>
+        <v>122773615</v>
       </c>
       <c r="B29" t="n">
         <v>57478</v>
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>438630</v>
+        <v>438145</v>
       </c>
       <c r="R29" t="n">
-        <v>7010427</v>
+        <v>7010332</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3762,7 +3762,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122773618</v>
+        <v>122773602</v>
       </c>
       <c r="B30" t="n">
         <v>57478</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>438180</v>
+        <v>438601</v>
       </c>
       <c r="R30" t="n">
-        <v>7010258</v>
+        <v>7010314</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3869,7 +3869,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122773614</v>
+        <v>122773600</v>
       </c>
       <c r="B31" t="n">
         <v>57478</v>
@@ -3909,10 +3909,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>438145</v>
+        <v>438630</v>
       </c>
       <c r="R31" t="n">
-        <v>7010359</v>
+        <v>7010427</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3949,7 +3949,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3976,7 +3976,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122773601</v>
+        <v>122773596</v>
       </c>
       <c r="B32" t="n">
         <v>57478</v>
@@ -4016,10 +4016,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>438600</v>
+        <v>438245</v>
       </c>
       <c r="R32" t="n">
-        <v>7010330</v>
+        <v>7010805</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4083,7 +4083,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122773596</v>
+        <v>122773607</v>
       </c>
       <c r="B33" t="n">
         <v>57478</v>
@@ -4123,10 +4123,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>438245</v>
+        <v>438336</v>
       </c>
       <c r="R33" t="n">
-        <v>7010805</v>
+        <v>7010625</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4163,7 +4163,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4190,7 +4190,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122773599</v>
+        <v>122773612</v>
       </c>
       <c r="B34" t="n">
         <v>57478</v>
@@ -4230,10 +4230,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>438431</v>
+        <v>438085</v>
       </c>
       <c r="R34" t="n">
-        <v>7010633</v>
+        <v>7010568</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 57504-2024 artfynd.xlsx
+++ b/artfynd/A 57504-2024 artfynd.xlsx
@@ -1822,10 +1822,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122773604</v>
+        <v>122773592</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>90952</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1838,21 +1838,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>438531</v>
+        <v>438283</v>
       </c>
       <c r="R12" t="n">
-        <v>7010323</v>
+        <v>7010189</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1898,11 +1898,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1929,7 +1924,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122773619</v>
+        <v>122773604</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1969,10 +1964,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>438283</v>
+        <v>438531</v>
       </c>
       <c r="R13" t="n">
-        <v>7010189</v>
+        <v>7010323</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2009,7 +2004,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2036,10 +2031,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122773592</v>
+        <v>122773619</v>
       </c>
       <c r="B14" t="n">
-        <v>90952</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2052,21 +2047,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2112,6 +2107,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 57504-2024 artfynd.xlsx
+++ b/artfynd/A 57504-2024 artfynd.xlsx
@@ -1608,7 +1608,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122773599</v>
+        <v>122773607</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>438431</v>
+        <v>438336</v>
       </c>
       <c r="R10" t="n">
-        <v>7010633</v>
+        <v>7010625</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1715,7 +1715,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122773616</v>
+        <v>122773609</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>438161</v>
+        <v>438318</v>
       </c>
       <c r="R11" t="n">
-        <v>7010308</v>
+        <v>7010644</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1924,7 +1924,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122773604</v>
+        <v>122773617</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>438531</v>
+        <v>438166</v>
       </c>
       <c r="R13" t="n">
-        <v>7010323</v>
+        <v>7010295</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2031,7 +2031,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122773619</v>
+        <v>122773614</v>
       </c>
       <c r="B14" t="n">
         <v>57478</v>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>438283</v>
+        <v>438145</v>
       </c>
       <c r="R14" t="n">
-        <v>7010189</v>
+        <v>7010359</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2138,7 +2138,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122773609</v>
+        <v>122773616</v>
       </c>
       <c r="B15" t="n">
         <v>57478</v>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>438318</v>
+        <v>438161</v>
       </c>
       <c r="R15" t="n">
-        <v>7010644</v>
+        <v>7010308</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2245,10 +2245,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122773617</v>
+        <v>122773626</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2261,21 +2261,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>438166</v>
+        <v>438169</v>
       </c>
       <c r="R16" t="n">
-        <v>7010295</v>
+        <v>7010796</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2352,7 +2352,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122773597</v>
+        <v>122773605</v>
       </c>
       <c r="B17" t="n">
         <v>57478</v>
@@ -2392,10 +2392,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>438355</v>
+        <v>438538</v>
       </c>
       <c r="R17" t="n">
-        <v>7010686</v>
+        <v>7010447</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2459,7 +2459,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122773598</v>
+        <v>122773612</v>
       </c>
       <c r="B18" t="n">
         <v>57478</v>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>438360</v>
+        <v>438085</v>
       </c>
       <c r="R18" t="n">
-        <v>7010674</v>
+        <v>7010568</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2566,10 +2566,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122773595</v>
+        <v>122773624</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2582,34 +2582,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>438193</v>
+        <v>438215</v>
       </c>
       <c r="R19" t="n">
-        <v>7010800</v>
+        <v>7010784</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2646,7 +2658,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 6 st</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2673,7 +2685,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122773601</v>
+        <v>122773618</v>
       </c>
       <c r="B20" t="n">
         <v>57478</v>
@@ -2713,10 +2725,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>438600</v>
+        <v>438180</v>
       </c>
       <c r="R20" t="n">
-        <v>7010330</v>
+        <v>7010258</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2753,7 +2765,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2780,10 +2792,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122773624</v>
+        <v>122773600</v>
       </c>
       <c r="B21" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2796,46 +2808,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>438215</v>
+        <v>438630</v>
       </c>
       <c r="R21" t="n">
-        <v>7010784</v>
+        <v>7010427</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Minst 6 st</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2899,7 +2899,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122773618</v>
+        <v>122773615</v>
       </c>
       <c r="B22" t="n">
         <v>57478</v>
@@ -2939,10 +2939,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>438180</v>
+        <v>438145</v>
       </c>
       <c r="R22" t="n">
-        <v>7010258</v>
+        <v>7010332</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3006,7 +3006,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122773614</v>
+        <v>122773595</v>
       </c>
       <c r="B23" t="n">
         <v>57478</v>
@@ -3046,10 +3046,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>438145</v>
+        <v>438193</v>
       </c>
       <c r="R23" t="n">
-        <v>7010359</v>
+        <v>7010800</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3113,7 +3113,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122773613</v>
+        <v>122773601</v>
       </c>
       <c r="B24" t="n">
         <v>57478</v>
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>438083</v>
+        <v>438600</v>
       </c>
       <c r="R24" t="n">
-        <v>7010509</v>
+        <v>7010330</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3220,10 +3220,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122773626</v>
+        <v>122773597</v>
       </c>
       <c r="B25" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3236,21 +3236,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3260,10 +3260,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>438169</v>
+        <v>438355</v>
       </c>
       <c r="R25" t="n">
-        <v>7010796</v>
+        <v>7010686</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3327,10 +3327,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122773591</v>
+        <v>122773613</v>
       </c>
       <c r="B26" t="n">
-        <v>90952</v>
+        <v>57478</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3343,21 +3343,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>438161</v>
+        <v>438083</v>
       </c>
       <c r="R26" t="n">
-        <v>7010308</v>
+        <v>7010509</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3403,6 +3403,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3429,7 +3434,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122773605</v>
+        <v>122773604</v>
       </c>
       <c r="B27" t="n">
         <v>57478</v>
@@ -3469,10 +3474,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>438538</v>
+        <v>438531</v>
       </c>
       <c r="R27" t="n">
-        <v>7010447</v>
+        <v>7010323</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3509,7 +3514,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3655,7 +3660,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122773615</v>
+        <v>122773596</v>
       </c>
       <c r="B29" t="n">
         <v>57478</v>
@@ -3695,10 +3700,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>438145</v>
+        <v>438245</v>
       </c>
       <c r="R29" t="n">
-        <v>7010332</v>
+        <v>7010805</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3735,7 +3740,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3762,7 +3767,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122773602</v>
+        <v>122773598</v>
       </c>
       <c r="B30" t="n">
         <v>57478</v>
@@ -3802,10 +3807,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>438601</v>
+        <v>438360</v>
       </c>
       <c r="R30" t="n">
-        <v>7010314</v>
+        <v>7010674</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3842,7 +3847,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3869,7 +3874,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122773600</v>
+        <v>122773619</v>
       </c>
       <c r="B31" t="n">
         <v>57478</v>
@@ -3909,10 +3914,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>438630</v>
+        <v>438283</v>
       </c>
       <c r="R31" t="n">
-        <v>7010427</v>
+        <v>7010189</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3976,7 +3981,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122773596</v>
+        <v>122773602</v>
       </c>
       <c r="B32" t="n">
         <v>57478</v>
@@ -4016,10 +4021,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>438245</v>
+        <v>438601</v>
       </c>
       <c r="R32" t="n">
-        <v>7010805</v>
+        <v>7010314</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4083,7 +4088,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122773607</v>
+        <v>122773599</v>
       </c>
       <c r="B33" t="n">
         <v>57478</v>
@@ -4123,10 +4128,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>438336</v>
+        <v>438431</v>
       </c>
       <c r="R33" t="n">
-        <v>7010625</v>
+        <v>7010633</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4190,10 +4195,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122773612</v>
+        <v>122773591</v>
       </c>
       <c r="B34" t="n">
-        <v>57478</v>
+        <v>90952</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4206,21 +4211,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4230,10 +4235,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>438085</v>
+        <v>438161</v>
       </c>
       <c r="R34" t="n">
-        <v>7010568</v>
+        <v>7010308</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4266,11 +4271,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 57504-2024 artfynd.xlsx
+++ b/artfynd/A 57504-2024 artfynd.xlsx
@@ -1924,7 +1924,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122773617</v>
+        <v>122773614</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>438166</v>
+        <v>438145</v>
       </c>
       <c r="R13" t="n">
-        <v>7010295</v>
+        <v>7010359</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2031,7 +2031,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122773614</v>
+        <v>122773617</v>
       </c>
       <c r="B14" t="n">
         <v>57478</v>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>438145</v>
+        <v>438166</v>
       </c>
       <c r="R14" t="n">
-        <v>7010359</v>
+        <v>7010295</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 57504-2024 artfynd.xlsx
+++ b/artfynd/A 57504-2024 artfynd.xlsx
@@ -1924,7 +1924,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122773614</v>
+        <v>122773617</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>438145</v>
+        <v>438166</v>
       </c>
       <c r="R13" t="n">
-        <v>7010359</v>
+        <v>7010295</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2031,7 +2031,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122773617</v>
+        <v>122773614</v>
       </c>
       <c r="B14" t="n">
         <v>57478</v>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>438166</v>
+        <v>438145</v>
       </c>
       <c r="R14" t="n">
-        <v>7010295</v>
+        <v>7010359</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2245,10 +2245,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122773626</v>
+        <v>122773605</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2261,21 +2261,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>438169</v>
+        <v>438538</v>
       </c>
       <c r="R16" t="n">
-        <v>7010796</v>
+        <v>7010447</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2352,7 +2352,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122773605</v>
+        <v>122773612</v>
       </c>
       <c r="B17" t="n">
         <v>57478</v>
@@ -2392,10 +2392,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>438538</v>
+        <v>438085</v>
       </c>
       <c r="R17" t="n">
-        <v>7010447</v>
+        <v>7010568</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2459,10 +2459,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122773612</v>
+        <v>122773626</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2475,21 +2475,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>438085</v>
+        <v>438169</v>
       </c>
       <c r="R18" t="n">
-        <v>7010568</v>
+        <v>7010796</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 57504-2024 artfynd.xlsx
+++ b/artfynd/A 57504-2024 artfynd.xlsx
@@ -1608,7 +1608,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122773607</v>
+        <v>122773605</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>438336</v>
+        <v>438538</v>
       </c>
       <c r="R10" t="n">
-        <v>7010625</v>
+        <v>7010447</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1715,7 +1715,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122773609</v>
+        <v>122773602</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>438318</v>
+        <v>438601</v>
       </c>
       <c r="R11" t="n">
-        <v>7010644</v>
+        <v>7010314</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1822,10 +1822,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122773592</v>
+        <v>122773624</v>
       </c>
       <c r="B12" t="n">
-        <v>90952</v>
+        <v>57631</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1838,34 +1838,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>438283</v>
+        <v>438215</v>
       </c>
       <c r="R12" t="n">
-        <v>7010189</v>
+        <v>7010784</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1898,6 +1910,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Minst 6 st</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1924,10 +1941,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122773617</v>
+        <v>122773625</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1940,16 +1957,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1957,17 +1974,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>438166</v>
+        <v>438106</v>
       </c>
       <c r="R13" t="n">
-        <v>7010295</v>
+        <v>7010492</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2004,7 +2033,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Hackande/trummande</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2031,7 +2060,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122773614</v>
+        <v>122773616</v>
       </c>
       <c r="B14" t="n">
         <v>57478</v>
@@ -2071,10 +2100,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>438145</v>
+        <v>438161</v>
       </c>
       <c r="R14" t="n">
-        <v>7010359</v>
+        <v>7010308</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2111,7 +2140,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2138,7 +2167,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122773616</v>
+        <v>122773604</v>
       </c>
       <c r="B15" t="n">
         <v>57478</v>
@@ -2178,10 +2207,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>438161</v>
+        <v>438531</v>
       </c>
       <c r="R15" t="n">
-        <v>7010308</v>
+        <v>7010323</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2218,7 +2247,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2245,7 +2274,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122773605</v>
+        <v>122773599</v>
       </c>
       <c r="B16" t="n">
         <v>57478</v>
@@ -2285,10 +2314,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>438538</v>
+        <v>438431</v>
       </c>
       <c r="R16" t="n">
-        <v>7010447</v>
+        <v>7010633</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2325,7 +2354,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2352,7 +2381,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122773612</v>
+        <v>122773619</v>
       </c>
       <c r="B17" t="n">
         <v>57478</v>
@@ -2392,10 +2421,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>438085</v>
+        <v>438283</v>
       </c>
       <c r="R17" t="n">
-        <v>7010568</v>
+        <v>7010189</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2432,7 +2461,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2459,10 +2488,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122773626</v>
+        <v>122773607</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2475,21 +2504,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2499,10 +2528,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>438169</v>
+        <v>438336</v>
       </c>
       <c r="R18" t="n">
-        <v>7010796</v>
+        <v>7010625</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2539,7 +2568,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2566,10 +2595,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122773624</v>
+        <v>122773617</v>
       </c>
       <c r="B19" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2582,46 +2611,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>438215</v>
+        <v>438166</v>
       </c>
       <c r="R19" t="n">
-        <v>7010784</v>
+        <v>7010295</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2658,7 +2675,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Minst 6 st</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2685,7 +2702,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122773618</v>
+        <v>122773615</v>
       </c>
       <c r="B20" t="n">
         <v>57478</v>
@@ -2725,10 +2742,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>438180</v>
+        <v>438145</v>
       </c>
       <c r="R20" t="n">
-        <v>7010258</v>
+        <v>7010332</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2765,7 +2782,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2792,7 +2809,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122773600</v>
+        <v>122773597</v>
       </c>
       <c r="B21" t="n">
         <v>57478</v>
@@ -2832,10 +2849,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>438630</v>
+        <v>438355</v>
       </c>
       <c r="R21" t="n">
-        <v>7010427</v>
+        <v>7010686</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2872,7 +2889,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2899,7 +2916,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122773615</v>
+        <v>122773596</v>
       </c>
       <c r="B22" t="n">
         <v>57478</v>
@@ -2939,10 +2956,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>438145</v>
+        <v>438245</v>
       </c>
       <c r="R22" t="n">
-        <v>7010332</v>
+        <v>7010805</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2979,7 +2996,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3006,7 +3023,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122773595</v>
+        <v>122773601</v>
       </c>
       <c r="B23" t="n">
         <v>57478</v>
@@ -3046,10 +3063,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>438193</v>
+        <v>438600</v>
       </c>
       <c r="R23" t="n">
-        <v>7010800</v>
+        <v>7010330</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3113,7 +3130,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122773601</v>
+        <v>122773598</v>
       </c>
       <c r="B24" t="n">
         <v>57478</v>
@@ -3153,10 +3170,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>438600</v>
+        <v>438360</v>
       </c>
       <c r="R24" t="n">
-        <v>7010330</v>
+        <v>7010674</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3220,7 +3237,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122773597</v>
+        <v>122773614</v>
       </c>
       <c r="B25" t="n">
         <v>57478</v>
@@ -3260,10 +3277,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>438355</v>
+        <v>438145</v>
       </c>
       <c r="R25" t="n">
-        <v>7010686</v>
+        <v>7010359</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3300,7 +3317,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3434,10 +3451,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122773604</v>
+        <v>122773626</v>
       </c>
       <c r="B27" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3450,21 +3467,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3474,10 +3491,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>438531</v>
+        <v>438169</v>
       </c>
       <c r="R27" t="n">
-        <v>7010323</v>
+        <v>7010796</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3514,7 +3531,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3541,10 +3558,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122773625</v>
+        <v>122773595</v>
       </c>
       <c r="B28" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3557,16 +3574,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3574,29 +3591,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>438106</v>
+        <v>438193</v>
       </c>
       <c r="R28" t="n">
-        <v>7010492</v>
+        <v>7010800</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3633,7 +3638,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Hackande/trummande</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3660,10 +3665,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122773596</v>
+        <v>122773592</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>90952</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3676,21 +3681,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3700,10 +3705,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>438245</v>
+        <v>438283</v>
       </c>
       <c r="R29" t="n">
-        <v>7010805</v>
+        <v>7010189</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3736,11 +3741,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3767,7 +3767,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122773598</v>
+        <v>122773612</v>
       </c>
       <c r="B30" t="n">
         <v>57478</v>
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>438360</v>
+        <v>438085</v>
       </c>
       <c r="R30" t="n">
-        <v>7010674</v>
+        <v>7010568</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3847,7 +3847,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3874,7 +3874,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122773619</v>
+        <v>122773618</v>
       </c>
       <c r="B31" t="n">
         <v>57478</v>
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>438283</v>
+        <v>438180</v>
       </c>
       <c r="R31" t="n">
-        <v>7010189</v>
+        <v>7010258</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3981,7 +3981,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122773602</v>
+        <v>122773609</v>
       </c>
       <c r="B32" t="n">
         <v>57478</v>
@@ -4021,10 +4021,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>438601</v>
+        <v>438318</v>
       </c>
       <c r="R32" t="n">
-        <v>7010314</v>
+        <v>7010644</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4088,10 +4088,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122773599</v>
+        <v>122773591</v>
       </c>
       <c r="B33" t="n">
-        <v>57478</v>
+        <v>90952</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4104,21 +4104,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>438431</v>
+        <v>438161</v>
       </c>
       <c r="R33" t="n">
-        <v>7010633</v>
+        <v>7010308</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4164,11 +4164,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4195,10 +4190,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122773591</v>
+        <v>122773600</v>
       </c>
       <c r="B34" t="n">
-        <v>90952</v>
+        <v>57478</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4211,21 +4206,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4235,10 +4230,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>438161</v>
+        <v>438630</v>
       </c>
       <c r="R34" t="n">
-        <v>7010308</v>
+        <v>7010427</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4271,6 +4266,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 57504-2024 artfynd.xlsx
+++ b/artfynd/A 57504-2024 artfynd.xlsx
@@ -1608,7 +1608,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122773605</v>
+        <v>122773618</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>438538</v>
+        <v>438180</v>
       </c>
       <c r="R10" t="n">
-        <v>7010447</v>
+        <v>7010258</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1715,7 +1715,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122773602</v>
+        <v>122773613</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>438601</v>
+        <v>438083</v>
       </c>
       <c r="R11" t="n">
-        <v>7010314</v>
+        <v>7010509</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1822,10 +1822,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122773624</v>
+        <v>122773600</v>
       </c>
       <c r="B12" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1838,46 +1838,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>438215</v>
+        <v>438630</v>
       </c>
       <c r="R12" t="n">
-        <v>7010784</v>
+        <v>7010427</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1914,7 +1902,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Minst 6 st</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1941,10 +1929,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122773625</v>
+        <v>122773602</v>
       </c>
       <c r="B13" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1957,16 +1945,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1974,29 +1962,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>438106</v>
+        <v>438601</v>
       </c>
       <c r="R13" t="n">
-        <v>7010492</v>
+        <v>7010314</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2033,7 +2009,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Hackande/trummande</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2060,7 +2036,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122773616</v>
+        <v>122773619</v>
       </c>
       <c r="B14" t="n">
         <v>57478</v>
@@ -2100,10 +2076,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>438161</v>
+        <v>438283</v>
       </c>
       <c r="R14" t="n">
-        <v>7010308</v>
+        <v>7010189</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2167,7 +2143,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122773604</v>
+        <v>122773601</v>
       </c>
       <c r="B15" t="n">
         <v>57478</v>
@@ -2207,10 +2183,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>438531</v>
+        <v>438600</v>
       </c>
       <c r="R15" t="n">
-        <v>7010323</v>
+        <v>7010330</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2274,7 +2250,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122773599</v>
+        <v>122773614</v>
       </c>
       <c r="B16" t="n">
         <v>57478</v>
@@ -2314,10 +2290,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>438431</v>
+        <v>438145</v>
       </c>
       <c r="R16" t="n">
-        <v>7010633</v>
+        <v>7010359</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2381,7 +2357,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122773619</v>
+        <v>122773616</v>
       </c>
       <c r="B17" t="n">
         <v>57478</v>
@@ -2421,10 +2397,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>438283</v>
+        <v>438161</v>
       </c>
       <c r="R17" t="n">
-        <v>7010189</v>
+        <v>7010308</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2488,7 +2464,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122773607</v>
+        <v>122773605</v>
       </c>
       <c r="B18" t="n">
         <v>57478</v>
@@ -2528,10 +2504,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>438336</v>
+        <v>438538</v>
       </c>
       <c r="R18" t="n">
-        <v>7010625</v>
+        <v>7010447</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2568,7 +2544,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2595,10 +2571,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122773617</v>
+        <v>122773625</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2611,16 +2587,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2628,17 +2604,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>438166</v>
+        <v>438106</v>
       </c>
       <c r="R19" t="n">
-        <v>7010295</v>
+        <v>7010492</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2675,7 +2663,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Hackande/trummande</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2702,7 +2690,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122773615</v>
+        <v>122773612</v>
       </c>
       <c r="B20" t="n">
         <v>57478</v>
@@ -2742,10 +2730,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>438145</v>
+        <v>438085</v>
       </c>
       <c r="R20" t="n">
-        <v>7010332</v>
+        <v>7010568</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2782,7 +2770,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2809,10 +2797,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122773597</v>
+        <v>122773624</v>
       </c>
       <c r="B21" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2825,34 +2813,46 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>438355</v>
+        <v>438215</v>
       </c>
       <c r="R21" t="n">
-        <v>7010686</v>
+        <v>7010784</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Minst 6 st</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2916,7 +2916,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122773596</v>
+        <v>122773615</v>
       </c>
       <c r="B22" t="n">
         <v>57478</v>
@@ -2956,10 +2956,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>438245</v>
+        <v>438145</v>
       </c>
       <c r="R22" t="n">
-        <v>7010805</v>
+        <v>7010332</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3023,10 +3023,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122773601</v>
+        <v>122773626</v>
       </c>
       <c r="B23" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3039,21 +3039,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>438600</v>
+        <v>438169</v>
       </c>
       <c r="R23" t="n">
-        <v>7010330</v>
+        <v>7010796</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3130,7 +3130,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122773598</v>
+        <v>122773607</v>
       </c>
       <c r="B24" t="n">
         <v>57478</v>
@@ -3170,10 +3170,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>438360</v>
+        <v>438336</v>
       </c>
       <c r="R24" t="n">
-        <v>7010674</v>
+        <v>7010625</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3237,7 +3237,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122773614</v>
+        <v>122773599</v>
       </c>
       <c r="B25" t="n">
         <v>57478</v>
@@ -3277,10 +3277,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>438145</v>
+        <v>438431</v>
       </c>
       <c r="R25" t="n">
-        <v>7010359</v>
+        <v>7010633</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3344,10 +3344,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122773613</v>
+        <v>122773592</v>
       </c>
       <c r="B26" t="n">
-        <v>57478</v>
+        <v>90952</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3360,21 +3360,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3384,10 +3384,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>438083</v>
+        <v>438283</v>
       </c>
       <c r="R26" t="n">
-        <v>7010509</v>
+        <v>7010189</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3420,11 +3420,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3451,10 +3446,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122773626</v>
+        <v>122773597</v>
       </c>
       <c r="B27" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3467,21 +3462,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3491,10 +3486,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>438169</v>
+        <v>438355</v>
       </c>
       <c r="R27" t="n">
-        <v>7010796</v>
+        <v>7010686</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3531,7 +3526,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3665,10 +3660,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122773592</v>
+        <v>122773598</v>
       </c>
       <c r="B29" t="n">
-        <v>90952</v>
+        <v>57478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3681,21 +3676,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3705,10 +3700,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>438283</v>
+        <v>438360</v>
       </c>
       <c r="R29" t="n">
-        <v>7010189</v>
+        <v>7010674</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3741,6 +3736,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3767,7 +3767,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122773612</v>
+        <v>122773604</v>
       </c>
       <c r="B30" t="n">
         <v>57478</v>
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>438085</v>
+        <v>438531</v>
       </c>
       <c r="R30" t="n">
-        <v>7010568</v>
+        <v>7010323</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3847,7 +3847,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3874,7 +3874,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122773618</v>
+        <v>122773617</v>
       </c>
       <c r="B31" t="n">
         <v>57478</v>
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>438180</v>
+        <v>438166</v>
       </c>
       <c r="R31" t="n">
-        <v>7010258</v>
+        <v>7010295</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3981,10 +3981,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122773609</v>
+        <v>122773591</v>
       </c>
       <c r="B32" t="n">
-        <v>57478</v>
+        <v>90952</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3997,21 +3997,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4021,10 +4021,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>438318</v>
+        <v>438161</v>
       </c>
       <c r="R32" t="n">
-        <v>7010644</v>
+        <v>7010308</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4057,11 +4057,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4088,10 +4083,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122773591</v>
+        <v>122773596</v>
       </c>
       <c r="B33" t="n">
-        <v>90952</v>
+        <v>57478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4104,21 +4099,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4128,10 +4123,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>438161</v>
+        <v>438245</v>
       </c>
       <c r="R33" t="n">
-        <v>7010308</v>
+        <v>7010805</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4164,6 +4159,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4190,7 +4190,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122773600</v>
+        <v>122773609</v>
       </c>
       <c r="B34" t="n">
         <v>57478</v>
@@ -4230,10 +4230,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>438630</v>
+        <v>438318</v>
       </c>
       <c r="R34" t="n">
-        <v>7010427</v>
+        <v>7010644</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 57504-2024 artfynd.xlsx
+++ b/artfynd/A 57504-2024 artfynd.xlsx
@@ -1608,10 +1608,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122773618</v>
+        <v>122773613</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>438180</v>
+        <v>438083</v>
       </c>
       <c r="R10" t="n">
-        <v>7010258</v>
+        <v>7010509</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1715,10 +1715,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122773613</v>
+        <v>122773604</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>438083</v>
+        <v>438531</v>
       </c>
       <c r="R11" t="n">
-        <v>7010509</v>
+        <v>7010323</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122773600</v>
+        <v>122773601</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>438630</v>
+        <v>438600</v>
       </c>
       <c r="R12" t="n">
-        <v>7010427</v>
+        <v>7010330</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1929,10 +1929,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122773602</v>
+        <v>122773616</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1969,10 +1969,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>438601</v>
+        <v>438161</v>
       </c>
       <c r="R13" t="n">
-        <v>7010314</v>
+        <v>7010308</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2036,10 +2036,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122773619</v>
+        <v>122773592</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>90955</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2052,21 +2052,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2112,11 +2112,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2143,10 +2138,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122773601</v>
+        <v>122773591</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>90955</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2159,21 +2154,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2183,10 +2178,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>438600</v>
+        <v>438161</v>
       </c>
       <c r="R15" t="n">
-        <v>7010330</v>
+        <v>7010308</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2219,11 +2214,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2250,10 +2240,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122773614</v>
+        <v>122773595</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2290,10 +2280,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>438145</v>
+        <v>438193</v>
       </c>
       <c r="R16" t="n">
-        <v>7010359</v>
+        <v>7010800</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2357,10 +2347,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122773616</v>
+        <v>122773624</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>57634</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2373,34 +2363,46 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>438161</v>
+        <v>438215</v>
       </c>
       <c r="R17" t="n">
-        <v>7010308</v>
+        <v>7010784</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2437,7 +2439,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Minst 6 st</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2464,10 +2466,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122773605</v>
+        <v>122773619</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2504,10 +2506,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>438538</v>
+        <v>438283</v>
       </c>
       <c r="R18" t="n">
-        <v>7010447</v>
+        <v>7010189</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2544,7 +2546,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2571,10 +2573,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122773625</v>
+        <v>122773602</v>
       </c>
       <c r="B19" t="n">
-        <v>57494</v>
+        <v>57481</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2587,16 +2589,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2604,29 +2606,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>438106</v>
+        <v>438601</v>
       </c>
       <c r="R19" t="n">
-        <v>7010492</v>
+        <v>7010314</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2663,7 +2653,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Hackande/trummande</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2690,10 +2680,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122773612</v>
+        <v>122773609</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2730,10 +2720,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>438085</v>
+        <v>438318</v>
       </c>
       <c r="R20" t="n">
-        <v>7010568</v>
+        <v>7010644</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2770,7 +2760,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2797,10 +2787,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122773624</v>
+        <v>122773614</v>
       </c>
       <c r="B21" t="n">
-        <v>57631</v>
+        <v>57481</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2813,46 +2803,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>438215</v>
+        <v>438145</v>
       </c>
       <c r="R21" t="n">
-        <v>7010784</v>
+        <v>7010359</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2889,7 +2867,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Minst 6 st</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2916,10 +2894,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122773615</v>
+        <v>122773605</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2956,10 +2934,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>438145</v>
+        <v>438538</v>
       </c>
       <c r="R22" t="n">
-        <v>7010332</v>
+        <v>7010447</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2996,7 +2974,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3023,10 +3001,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122773626</v>
+        <v>122773600</v>
       </c>
       <c r="B23" t="n">
-        <v>78766</v>
+        <v>57481</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3039,21 +3017,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3063,10 +3041,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>438169</v>
+        <v>438630</v>
       </c>
       <c r="R23" t="n">
-        <v>7010796</v>
+        <v>7010427</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3103,7 +3081,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3130,10 +3108,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122773607</v>
+        <v>122773617</v>
       </c>
       <c r="B24" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3170,10 +3148,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>438336</v>
+        <v>438166</v>
       </c>
       <c r="R24" t="n">
-        <v>7010625</v>
+        <v>7010295</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3210,7 +3188,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3237,10 +3215,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122773599</v>
+        <v>122773626</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>78769</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3253,21 +3231,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3277,10 +3255,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>438431</v>
+        <v>438169</v>
       </c>
       <c r="R25" t="n">
-        <v>7010633</v>
+        <v>7010796</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3317,7 +3295,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3344,10 +3322,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122773592</v>
+        <v>122773612</v>
       </c>
       <c r="B26" t="n">
-        <v>90952</v>
+        <v>57481</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3360,21 +3338,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3384,10 +3362,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>438283</v>
+        <v>438085</v>
       </c>
       <c r="R26" t="n">
-        <v>7010189</v>
+        <v>7010568</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3420,6 +3398,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3446,10 +3429,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122773597</v>
+        <v>122773599</v>
       </c>
       <c r="B27" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3486,10 +3469,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>438355</v>
+        <v>438431</v>
       </c>
       <c r="R27" t="n">
-        <v>7010686</v>
+        <v>7010633</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3526,7 +3509,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3553,10 +3536,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122773595</v>
+        <v>122773596</v>
       </c>
       <c r="B28" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3593,10 +3576,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>438193</v>
+        <v>438245</v>
       </c>
       <c r="R28" t="n">
-        <v>7010800</v>
+        <v>7010805</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3633,7 +3616,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3660,10 +3643,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122773598</v>
+        <v>122773615</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3700,10 +3683,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>438360</v>
+        <v>438145</v>
       </c>
       <c r="R29" t="n">
-        <v>7010674</v>
+        <v>7010332</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3767,10 +3750,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122773604</v>
+        <v>122773598</v>
       </c>
       <c r="B30" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3807,10 +3790,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>438531</v>
+        <v>438360</v>
       </c>
       <c r="R30" t="n">
-        <v>7010323</v>
+        <v>7010674</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3874,10 +3857,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122773617</v>
+        <v>122773607</v>
       </c>
       <c r="B31" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3914,10 +3897,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>438166</v>
+        <v>438336</v>
       </c>
       <c r="R31" t="n">
-        <v>7010295</v>
+        <v>7010625</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3954,7 +3937,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3981,10 +3964,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122773591</v>
+        <v>122773625</v>
       </c>
       <c r="B32" t="n">
-        <v>90952</v>
+        <v>57497</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3997,34 +3980,46 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>438161</v>
+        <v>438106</v>
       </c>
       <c r="R32" t="n">
-        <v>7010308</v>
+        <v>7010492</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4057,6 +4052,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Hackande/trummande</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4083,10 +4083,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122773596</v>
+        <v>122773618</v>
       </c>
       <c r="B33" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4123,10 +4123,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>438245</v>
+        <v>438180</v>
       </c>
       <c r="R33" t="n">
-        <v>7010805</v>
+        <v>7010258</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4190,10 +4190,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122773609</v>
+        <v>122773597</v>
       </c>
       <c r="B34" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4230,10 +4230,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>438318</v>
+        <v>438355</v>
       </c>
       <c r="R34" t="n">
-        <v>7010644</v>
+        <v>7010686</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4300,7 +4300,7 @@
         <v>122797613</v>
       </c>
       <c r="B35" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>122773606</v>
       </c>
       <c r="B36" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>

--- a/artfynd/A 57504-2024 artfynd.xlsx
+++ b/artfynd/A 57504-2024 artfynd.xlsx
@@ -1608,10 +1608,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122773613</v>
+        <v>122773592</v>
       </c>
       <c r="B10" t="n">
-        <v>57481</v>
+        <v>90957</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1624,21 +1624,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>438083</v>
+        <v>438283</v>
       </c>
       <c r="R10" t="n">
-        <v>7010509</v>
+        <v>7010189</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1684,11 +1684,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1715,7 +1710,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122773604</v>
+        <v>122773609</v>
       </c>
       <c r="B11" t="n">
         <v>57481</v>
@@ -1755,10 +1750,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>438531</v>
+        <v>438318</v>
       </c>
       <c r="R11" t="n">
-        <v>7010323</v>
+        <v>7010644</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1822,7 +1817,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122773601</v>
+        <v>122773598</v>
       </c>
       <c r="B12" t="n">
         <v>57481</v>
@@ -1862,10 +1857,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>438600</v>
+        <v>438360</v>
       </c>
       <c r="R12" t="n">
-        <v>7010330</v>
+        <v>7010674</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1929,7 +1924,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122773616</v>
+        <v>122773619</v>
       </c>
       <c r="B13" t="n">
         <v>57481</v>
@@ -1969,10 +1964,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>438161</v>
+        <v>438283</v>
       </c>
       <c r="R13" t="n">
-        <v>7010308</v>
+        <v>7010189</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2036,10 +2031,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122773592</v>
+        <v>122773591</v>
       </c>
       <c r="B14" t="n">
-        <v>90955</v>
+        <v>90957</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2076,10 +2071,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>438283</v>
+        <v>438161</v>
       </c>
       <c r="R14" t="n">
-        <v>7010189</v>
+        <v>7010308</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2138,10 +2133,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122773591</v>
+        <v>122773626</v>
       </c>
       <c r="B15" t="n">
-        <v>90955</v>
+        <v>78771</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2154,21 +2149,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2178,10 +2173,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>438161</v>
+        <v>438169</v>
       </c>
       <c r="R15" t="n">
-        <v>7010308</v>
+        <v>7010796</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2214,6 +2209,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2466,7 +2466,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122773619</v>
+        <v>122773601</v>
       </c>
       <c r="B18" t="n">
         <v>57481</v>
@@ -2506,10 +2506,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>438283</v>
+        <v>438600</v>
       </c>
       <c r="R18" t="n">
-        <v>7010189</v>
+        <v>7010330</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2573,7 +2573,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122773602</v>
+        <v>122773604</v>
       </c>
       <c r="B19" t="n">
         <v>57481</v>
@@ -2613,10 +2613,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>438601</v>
+        <v>438531</v>
       </c>
       <c r="R19" t="n">
-        <v>7010314</v>
+        <v>7010323</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2680,10 +2680,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122773609</v>
+        <v>122773625</v>
       </c>
       <c r="B20" t="n">
-        <v>57481</v>
+        <v>57497</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2696,16 +2696,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2713,17 +2713,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>438318</v>
+        <v>438106</v>
       </c>
       <c r="R20" t="n">
-        <v>7010644</v>
+        <v>7010492</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2760,7 +2772,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hackande/trummande</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2787,7 +2799,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122773614</v>
+        <v>122773605</v>
       </c>
       <c r="B21" t="n">
         <v>57481</v>
@@ -2827,10 +2839,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>438145</v>
+        <v>438538</v>
       </c>
       <c r="R21" t="n">
-        <v>7010359</v>
+        <v>7010447</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2867,7 +2879,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2894,7 +2906,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122773605</v>
+        <v>122773607</v>
       </c>
       <c r="B22" t="n">
         <v>57481</v>
@@ -2934,10 +2946,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>438538</v>
+        <v>438336</v>
       </c>
       <c r="R22" t="n">
-        <v>7010447</v>
+        <v>7010625</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2974,7 +2986,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3001,7 +3013,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122773600</v>
+        <v>122773618</v>
       </c>
       <c r="B23" t="n">
         <v>57481</v>
@@ -3041,10 +3053,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>438630</v>
+        <v>438180</v>
       </c>
       <c r="R23" t="n">
-        <v>7010427</v>
+        <v>7010258</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3081,7 +3093,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3108,7 +3120,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122773617</v>
+        <v>122773596</v>
       </c>
       <c r="B24" t="n">
         <v>57481</v>
@@ -3148,10 +3160,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>438166</v>
+        <v>438245</v>
       </c>
       <c r="R24" t="n">
-        <v>7010295</v>
+        <v>7010805</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3215,10 +3227,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122773626</v>
+        <v>122773612</v>
       </c>
       <c r="B25" t="n">
-        <v>78769</v>
+        <v>57481</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3231,21 +3243,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3255,10 +3267,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>438169</v>
+        <v>438085</v>
       </c>
       <c r="R25" t="n">
-        <v>7010796</v>
+        <v>7010568</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3295,7 +3307,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3322,7 +3334,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122773612</v>
+        <v>122773617</v>
       </c>
       <c r="B26" t="n">
         <v>57481</v>
@@ -3362,10 +3374,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>438085</v>
+        <v>438166</v>
       </c>
       <c r="R26" t="n">
-        <v>7010568</v>
+        <v>7010295</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3429,7 +3441,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122773599</v>
+        <v>122773616</v>
       </c>
       <c r="B27" t="n">
         <v>57481</v>
@@ -3469,10 +3481,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>438431</v>
+        <v>438161</v>
       </c>
       <c r="R27" t="n">
-        <v>7010633</v>
+        <v>7010308</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3509,7 +3521,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3536,7 +3548,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122773596</v>
+        <v>122773615</v>
       </c>
       <c r="B28" t="n">
         <v>57481</v>
@@ -3576,10 +3588,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>438245</v>
+        <v>438145</v>
       </c>
       <c r="R28" t="n">
-        <v>7010805</v>
+        <v>7010332</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3616,7 +3628,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3643,7 +3655,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122773615</v>
+        <v>122773600</v>
       </c>
       <c r="B29" t="n">
         <v>57481</v>
@@ -3683,10 +3695,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>438145</v>
+        <v>438630</v>
       </c>
       <c r="R29" t="n">
-        <v>7010332</v>
+        <v>7010427</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3723,7 +3735,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3750,7 +3762,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122773598</v>
+        <v>122773597</v>
       </c>
       <c r="B30" t="n">
         <v>57481</v>
@@ -3790,10 +3802,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>438360</v>
+        <v>438355</v>
       </c>
       <c r="R30" t="n">
-        <v>7010674</v>
+        <v>7010686</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3830,7 +3842,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3857,7 +3869,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122773607</v>
+        <v>122773599</v>
       </c>
       <c r="B31" t="n">
         <v>57481</v>
@@ -3897,10 +3909,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>438336</v>
+        <v>438431</v>
       </c>
       <c r="R31" t="n">
-        <v>7010625</v>
+        <v>7010633</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3964,10 +3976,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122773625</v>
+        <v>122773614</v>
       </c>
       <c r="B32" t="n">
-        <v>57497</v>
+        <v>57481</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3980,16 +3992,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3997,29 +4009,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>438106</v>
+        <v>438145</v>
       </c>
       <c r="R32" t="n">
-        <v>7010492</v>
+        <v>7010359</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Hackande/trummande</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4083,7 +4083,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122773618</v>
+        <v>122773613</v>
       </c>
       <c r="B33" t="n">
         <v>57481</v>
@@ -4123,10 +4123,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>438180</v>
+        <v>438083</v>
       </c>
       <c r="R33" t="n">
-        <v>7010258</v>
+        <v>7010509</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4163,7 +4163,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4190,7 +4190,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122773597</v>
+        <v>122773602</v>
       </c>
       <c r="B34" t="n">
         <v>57481</v>
@@ -4230,10 +4230,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>438355</v>
+        <v>438601</v>
       </c>
       <c r="R34" t="n">
-        <v>7010686</v>
+        <v>7010314</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>

--- a/artfynd/A 57504-2024 artfynd.xlsx
+++ b/artfynd/A 57504-2024 artfynd.xlsx
@@ -2680,10 +2680,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122773625</v>
+        <v>122773605</v>
       </c>
       <c r="B20" t="n">
-        <v>57497</v>
+        <v>57481</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2696,16 +2696,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2713,29 +2713,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>438106</v>
+        <v>438538</v>
       </c>
       <c r="R20" t="n">
-        <v>7010492</v>
+        <v>7010447</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2772,7 +2760,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Hackande/trummande</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2799,7 +2787,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122773605</v>
+        <v>122773607</v>
       </c>
       <c r="B21" t="n">
         <v>57481</v>
@@ -2839,10 +2827,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>438538</v>
+        <v>438336</v>
       </c>
       <c r="R21" t="n">
-        <v>7010447</v>
+        <v>7010625</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2879,7 +2867,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2906,10 +2894,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122773607</v>
+        <v>122773625</v>
       </c>
       <c r="B22" t="n">
-        <v>57481</v>
+        <v>57497</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2922,16 +2910,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2939,17 +2927,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>438336</v>
+        <v>438106</v>
       </c>
       <c r="R22" t="n">
-        <v>7010625</v>
+        <v>7010492</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hackande/trummande</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 57504-2024 artfynd.xlsx
+++ b/artfynd/A 57504-2024 artfynd.xlsx
@@ -1608,10 +1608,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122773592</v>
+        <v>122773619</v>
       </c>
       <c r="B10" t="n">
-        <v>90957</v>
+        <v>57481</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1624,21 +1624,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1684,6 +1684,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,7 +1715,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122773609</v>
+        <v>122773601</v>
       </c>
       <c r="B11" t="n">
         <v>57481</v>
@@ -1750,10 +1755,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>438318</v>
+        <v>438600</v>
       </c>
       <c r="R11" t="n">
-        <v>7010644</v>
+        <v>7010330</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1817,10 +1822,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122773598</v>
+        <v>122773592</v>
       </c>
       <c r="B12" t="n">
-        <v>57481</v>
+        <v>90963</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1833,21 +1838,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1857,10 +1862,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>438360</v>
+        <v>438283</v>
       </c>
       <c r="R12" t="n">
-        <v>7010674</v>
+        <v>7010189</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1893,11 +1898,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1924,7 +1924,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122773619</v>
+        <v>122773615</v>
       </c>
       <c r="B13" t="n">
         <v>57481</v>
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>438283</v>
+        <v>438145</v>
       </c>
       <c r="R13" t="n">
-        <v>7010189</v>
+        <v>7010332</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2031,10 +2031,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122773591</v>
+        <v>122773599</v>
       </c>
       <c r="B14" t="n">
-        <v>90957</v>
+        <v>57481</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2047,21 +2047,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>438161</v>
+        <v>438431</v>
       </c>
       <c r="R14" t="n">
-        <v>7010308</v>
+        <v>7010633</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2107,6 +2107,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2136,7 +2141,7 @@
         <v>122773626</v>
       </c>
       <c r="B15" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2240,7 +2245,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122773595</v>
+        <v>122773614</v>
       </c>
       <c r="B16" t="n">
         <v>57481</v>
@@ -2280,10 +2285,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>438193</v>
+        <v>438145</v>
       </c>
       <c r="R16" t="n">
-        <v>7010800</v>
+        <v>7010359</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2347,10 +2352,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122773624</v>
+        <v>122773617</v>
       </c>
       <c r="B17" t="n">
-        <v>57634</v>
+        <v>57481</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2363,46 +2368,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>438215</v>
+        <v>438166</v>
       </c>
       <c r="R17" t="n">
-        <v>7010784</v>
+        <v>7010295</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2439,7 +2432,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Minst 6 st</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2466,7 +2459,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122773601</v>
+        <v>122773618</v>
       </c>
       <c r="B18" t="n">
         <v>57481</v>
@@ -2506,10 +2499,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>438600</v>
+        <v>438180</v>
       </c>
       <c r="R18" t="n">
-        <v>7010330</v>
+        <v>7010258</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2546,7 +2539,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2573,7 +2566,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122773604</v>
+        <v>122773598</v>
       </c>
       <c r="B19" t="n">
         <v>57481</v>
@@ -2613,10 +2606,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>438531</v>
+        <v>438360</v>
       </c>
       <c r="R19" t="n">
-        <v>7010323</v>
+        <v>7010674</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2680,10 +2673,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122773605</v>
+        <v>122773624</v>
       </c>
       <c r="B20" t="n">
-        <v>57481</v>
+        <v>57634</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2696,34 +2689,46 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>438538</v>
+        <v>438215</v>
       </c>
       <c r="R20" t="n">
-        <v>7010447</v>
+        <v>7010784</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2760,7 +2765,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Minst 6 st</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2787,7 +2792,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122773607</v>
+        <v>122773595</v>
       </c>
       <c r="B21" t="n">
         <v>57481</v>
@@ -2827,10 +2832,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>438336</v>
+        <v>438193</v>
       </c>
       <c r="R21" t="n">
-        <v>7010625</v>
+        <v>7010800</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2894,10 +2899,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122773625</v>
+        <v>122773616</v>
       </c>
       <c r="B22" t="n">
-        <v>57497</v>
+        <v>57481</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2910,16 +2915,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2927,29 +2932,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>438106</v>
+        <v>438161</v>
       </c>
       <c r="R22" t="n">
-        <v>7010492</v>
+        <v>7010308</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2986,7 +2979,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Hackande/trummande</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3013,7 +3006,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122773618</v>
+        <v>122773597</v>
       </c>
       <c r="B23" t="n">
         <v>57481</v>
@@ -3053,10 +3046,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>438180</v>
+        <v>438355</v>
       </c>
       <c r="R23" t="n">
-        <v>7010258</v>
+        <v>7010686</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3120,10 +3113,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122773596</v>
+        <v>122773625</v>
       </c>
       <c r="B24" t="n">
-        <v>57481</v>
+        <v>57497</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3136,16 +3129,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3153,17 +3146,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>438245</v>
+        <v>438106</v>
       </c>
       <c r="R24" t="n">
-        <v>7010805</v>
+        <v>7010492</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3200,7 +3205,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Hackande/trummande</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3227,7 +3232,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122773612</v>
+        <v>122773600</v>
       </c>
       <c r="B25" t="n">
         <v>57481</v>
@@ -3267,10 +3272,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>438085</v>
+        <v>438630</v>
       </c>
       <c r="R25" t="n">
-        <v>7010568</v>
+        <v>7010427</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3307,7 +3312,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3334,7 +3339,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122773617</v>
+        <v>122773607</v>
       </c>
       <c r="B26" t="n">
         <v>57481</v>
@@ -3374,10 +3379,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>438166</v>
+        <v>438336</v>
       </c>
       <c r="R26" t="n">
-        <v>7010295</v>
+        <v>7010625</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3414,7 +3419,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3441,7 +3446,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122773616</v>
+        <v>122773609</v>
       </c>
       <c r="B27" t="n">
         <v>57481</v>
@@ -3481,10 +3486,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>438161</v>
+        <v>438318</v>
       </c>
       <c r="R27" t="n">
-        <v>7010308</v>
+        <v>7010644</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3521,7 +3526,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3548,10 +3553,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122773615</v>
+        <v>122773591</v>
       </c>
       <c r="B28" t="n">
-        <v>57481</v>
+        <v>90963</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3564,21 +3569,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3588,10 +3593,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>438145</v>
+        <v>438161</v>
       </c>
       <c r="R28" t="n">
-        <v>7010332</v>
+        <v>7010308</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3624,11 +3629,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3655,7 +3655,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122773600</v>
+        <v>122773604</v>
       </c>
       <c r="B29" t="n">
         <v>57481</v>
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>438630</v>
+        <v>438531</v>
       </c>
       <c r="R29" t="n">
-        <v>7010427</v>
+        <v>7010323</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3762,7 +3762,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122773597</v>
+        <v>122773602</v>
       </c>
       <c r="B30" t="n">
         <v>57481</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>438355</v>
+        <v>438601</v>
       </c>
       <c r="R30" t="n">
-        <v>7010686</v>
+        <v>7010314</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3869,7 +3869,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122773599</v>
+        <v>122773596</v>
       </c>
       <c r="B31" t="n">
         <v>57481</v>
@@ -3909,10 +3909,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>438431</v>
+        <v>438245</v>
       </c>
       <c r="R31" t="n">
-        <v>7010633</v>
+        <v>7010805</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3949,7 +3949,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3976,7 +3976,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122773614</v>
+        <v>122773605</v>
       </c>
       <c r="B32" t="n">
         <v>57481</v>
@@ -4016,10 +4016,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>438145</v>
+        <v>438538</v>
       </c>
       <c r="R32" t="n">
-        <v>7010359</v>
+        <v>7010447</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4190,7 +4190,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122773602</v>
+        <v>122773612</v>
       </c>
       <c r="B34" t="n">
         <v>57481</v>
@@ -4230,10 +4230,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>438601</v>
+        <v>438085</v>
       </c>
       <c r="R34" t="n">
-        <v>7010314</v>
+        <v>7010568</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>

--- a/artfynd/A 57504-2024 artfynd.xlsx
+++ b/artfynd/A 57504-2024 artfynd.xlsx
@@ -4407,7 +4407,7 @@
         <v>122773606</v>
       </c>
       <c r="B36" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>

--- a/artfynd/A 57504-2024 artfynd.xlsx
+++ b/artfynd/A 57504-2024 artfynd.xlsx
@@ -4407,7 +4407,7 @@
         <v>122773606</v>
       </c>
       <c r="B36" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>

--- a/artfynd/A 57504-2024 artfynd.xlsx
+++ b/artfynd/A 57504-2024 artfynd.xlsx
@@ -4407,7 +4407,7 @@
         <v>122773606</v>
       </c>
       <c r="B36" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
